--- a/docx_templates/CONTAS-A-RECEBER.xlsx
+++ b/docx_templates/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$109</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$110</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="177">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em quinta-feira, 7 de maio de 2026 por KAROL MEDEIROS</t>
+    <t>Relatório exportado em sexta-feira, 8 de maio de 2026 por KAROL MEDEIROS</t>
   </si>
   <si>
     <t>Conta de Recebimento</t>
@@ -172,136 +172,328 @@
     <t>ANDRE CAVALCANTI DA FE</t>
   </si>
   <si>
+    <t>FA-11446</t>
+  </si>
+  <si>
+    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
+  </si>
+  <si>
+    <t>ND-11574</t>
+  </si>
+  <si>
+    <t>REGINALDO BENTO DA SILVA</t>
+  </si>
+  <si>
+    <t>HOJE</t>
+  </si>
+  <si>
+    <t>JOÃO PAULO CONSÓRCIOS</t>
+  </si>
+  <si>
+    <t>FA-11452</t>
+  </si>
+  <si>
+    <t>YAGO ELIAS COSTA BATISTA</t>
+  </si>
+  <si>
+    <t>FA-11410</t>
+  </si>
+  <si>
+    <t>DAVI HENRIQUE DANTAS DE SOUZA</t>
+  </si>
+  <si>
+    <t>A VENCER</t>
+  </si>
+  <si>
+    <t>FA-11255</t>
+  </si>
+  <si>
+    <t>FA-11461</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11460</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
+    <t>FA-11356</t>
+  </si>
+  <si>
+    <t>ANDERSON QUEIROZ PINHEIRO</t>
+  </si>
+  <si>
+    <t>FA-11458</t>
+  </si>
+  <si>
+    <t>VENCIDO ACIMA DE 90 DIAS</t>
+  </si>
+  <si>
+    <t>ND-10427</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
+    <t>FA-11464</t>
+  </si>
+  <si>
+    <t>FA-11555</t>
+  </si>
+  <si>
+    <t>FA-11553</t>
+  </si>
+  <si>
+    <t>YURI BATISTA DA COSTA</t>
+  </si>
+  <si>
+    <t>FA-11396</t>
+  </si>
+  <si>
+    <t>FA-11466</t>
+  </si>
+  <si>
+    <t>FA-11424</t>
+  </si>
+  <si>
+    <t>OLIZIEL DA SILVA CARDOSO</t>
+  </si>
+  <si>
+    <t>FA-11554</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11468</t>
+  </si>
+  <si>
+    <t>FA-11351</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-11354</t>
+  </si>
+  <si>
+    <t>FA-11614</t>
+  </si>
+  <si>
+    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11587</t>
+  </si>
+  <si>
+    <t>JACKSON CASSIANO VERISSIMO</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
+  </si>
+  <si>
+    <t>FA-11114</t>
+  </si>
+  <si>
+    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
+  </si>
+  <si>
+    <t>FA-11355</t>
+  </si>
+  <si>
     <t>FA-11496</t>
   </si>
   <si>
-    <t>FA-11446</t>
-  </si>
-  <si>
-    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
-  </si>
-  <si>
-    <t>ND-11574</t>
-  </si>
-  <si>
-    <t>REGINALDO BENTO DA SILVA</t>
-  </si>
-  <si>
-    <t>A VENCER</t>
-  </si>
-  <si>
-    <t>JOÃO PAULO CONSÓRCIOS</t>
-  </si>
-  <si>
-    <t>FA-11452</t>
-  </si>
-  <si>
-    <t>YAGO ELIAS COSTA BATISTA</t>
-  </si>
-  <si>
-    <t>FA-11410</t>
-  </si>
-  <si>
-    <t>DAVI HENRIQUE DANTAS DE SOUZA</t>
-  </si>
-  <si>
-    <t>FA-11255</t>
-  </si>
-  <si>
-    <t>FA-11461</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11460</t>
-  </si>
-  <si>
-    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
-  </si>
-  <si>
-    <t>FA-11356</t>
-  </si>
-  <si>
-    <t>ANDERSON QUEIROZ PINHEIRO</t>
-  </si>
-  <si>
-    <t>FA-11458</t>
-  </si>
-  <si>
-    <t>VENCIDO ACIMA DE 90 DIAS</t>
-  </si>
-  <si>
-    <t>ND-10427</t>
-  </si>
-  <si>
-    <t>RICARDO ARAUJO DE MIRANDA</t>
-  </si>
-  <si>
-    <t>FA-11464</t>
-  </si>
-  <si>
-    <t>FA-11555</t>
-  </si>
-  <si>
-    <t>FA-11553</t>
-  </si>
-  <si>
-    <t>YURI BATISTA DA COSTA</t>
-  </si>
-  <si>
-    <t>FA-11355</t>
-  </si>
-  <si>
-    <t>FA-11396</t>
-  </si>
-  <si>
-    <t>FA-11466</t>
-  </si>
-  <si>
-    <t>FA-11424</t>
-  </si>
-  <si>
-    <t>OLIZIEL DA SILVA CARDOSO</t>
-  </si>
-  <si>
-    <t>FA-11554</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11468</t>
-  </si>
-  <si>
-    <t>FA-11115</t>
-  </si>
-  <si>
-    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
-  </si>
-  <si>
-    <t>FA-11351</t>
-  </si>
-  <si>
-    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
-  </si>
-  <si>
-    <t>FA-11354</t>
-  </si>
-  <si>
-    <t>FA-11114</t>
-  </si>
-  <si>
-    <t>FA-11587</t>
-  </si>
-  <si>
-    <t>JACKSON CASSIANO VERISSIMO</t>
-  </si>
-  <si>
-    <t>HOJE</t>
-  </si>
-  <si>
-    <t>LUZ DIVINA LTDA</t>
+    <t>FA-11397</t>
+  </si>
+  <si>
+    <t>JOZILDO TARQUINO DE BRITO</t>
+  </si>
+  <si>
+    <t>FA-11471</t>
+  </si>
+  <si>
+    <t>FA-11522</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>FA-11557</t>
+  </si>
+  <si>
+    <t>FA-11556</t>
+  </si>
+  <si>
+    <t>FA-11476</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>FA-11398</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>FA-11399</t>
+  </si>
+  <si>
+    <t>FA-11492</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11523</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11615</t>
+  </si>
+  <si>
+    <t>FA-11502</t>
+  </si>
+  <si>
+    <t>WESCLY JEAN DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>FA-11473</t>
+  </si>
+  <si>
+    <t>FA-11278</t>
+  </si>
+  <si>
+    <t>FELIPE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11432</t>
+  </si>
+  <si>
+    <t>RAYANE ROBERTA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11475</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>FA-11478</t>
+  </si>
+  <si>
+    <t>FA-11558</t>
+  </si>
+  <si>
+    <t>FA-11472</t>
+  </si>
+  <si>
+    <t>FA-11327</t>
+  </si>
+  <si>
+    <t>MAICON LOPES SILVA</t>
+  </si>
+  <si>
+    <t>FA-11267</t>
+  </si>
+  <si>
+    <t>ANNY KATARINA ACIOLE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11599</t>
+  </si>
+  <si>
+    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>FA-11575</t>
+  </si>
+  <si>
+    <t>ADRIANO TEOTONIO DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11453</t>
+  </si>
+  <si>
+    <t>FA-11400</t>
+  </si>
+  <si>
+    <t>FA-11474</t>
+  </si>
+  <si>
+    <t>FA-11525</t>
+  </si>
+  <si>
+    <t>FA-11481</t>
+  </si>
+  <si>
+    <t>FA-11559</t>
+  </si>
+  <si>
+    <t>FA-11560</t>
+  </si>
+  <si>
+    <t>FA-11493</t>
+  </si>
+  <si>
+    <t>FA-11526</t>
+  </si>
+  <si>
+    <t>FA-11401</t>
+  </si>
+  <si>
+    <t>FA-11402</t>
+  </si>
+  <si>
+    <t>FA-11616</t>
+  </si>
+  <si>
+    <t>FA-11279</t>
+  </si>
+  <si>
+    <t>FA-11503</t>
+  </si>
+  <si>
+    <t>FA-11482</t>
+  </si>
+  <si>
+    <t>FA-11433</t>
+  </si>
+  <si>
+    <t>FA-11411</t>
+  </si>
+  <si>
+    <t>FA-11483</t>
+  </si>
+  <si>
+    <t>FA-11484</t>
+  </si>
+  <si>
+    <t>FA-11561</t>
+  </si>
+  <si>
+    <t>FA-11268</t>
+  </si>
+  <si>
+    <t>FA-11328</t>
+  </si>
+  <si>
+    <t>FA-11479</t>
+  </si>
+  <si>
+    <t>FA-11600</t>
+  </si>
+  <si>
+    <t>FA-11590</t>
+  </si>
+  <si>
+    <t>FA-11577</t>
   </si>
   <si>
     <t>FA-11611</t>
@@ -310,10 +502,58 @@
     <t>M&amp;S DO TRABALHO</t>
   </si>
   <si>
-    <t>FA-11612</t>
-  </si>
-  <si>
-    <t>NEW CHARGER</t>
+    <t>FA-11480</t>
+  </si>
+  <si>
+    <t>FA-11562</t>
+  </si>
+  <si>
+    <t>FA-11563</t>
+  </si>
+  <si>
+    <t>FA-11487</t>
+  </si>
+  <si>
+    <t>FA-11494</t>
+  </si>
+  <si>
+    <t>FA-11617</t>
+  </si>
+  <si>
+    <t>FA-11488</t>
+  </si>
+  <si>
+    <t>FA-11504</t>
+  </si>
+  <si>
+    <t>FA-11280</t>
+  </si>
+  <si>
+    <t>FA-11434</t>
+  </si>
+  <si>
+    <t>FA-11412</t>
+  </si>
+  <si>
+    <t>FA-11489</t>
+  </si>
+  <si>
+    <t>FA-11491</t>
+  </si>
+  <si>
+    <t>FA-11564</t>
+  </si>
+  <si>
+    <t>FA-11329</t>
+  </si>
+  <si>
+    <t>FA-11601</t>
+  </si>
+  <si>
+    <t>FA-11591</t>
+  </si>
+  <si>
+    <t>FA-11578</t>
   </si>
   <si>
     <t>FA-11613</t>
@@ -323,243 +563,6 @@
   </si>
   <si>
     <t>SEGCOMP TECNOLOGIA LTDA</t>
-  </si>
-  <si>
-    <t>FA-11397</t>
-  </si>
-  <si>
-    <t>JOZILDO TARQUINO DE BRITO</t>
-  </si>
-  <si>
-    <t>FA-11471</t>
-  </si>
-  <si>
-    <t>FA-11522</t>
-  </si>
-  <si>
-    <t>ROBERTO MURATORI</t>
-  </si>
-  <si>
-    <t>FA-11557</t>
-  </si>
-  <si>
-    <t>FA-11556</t>
-  </si>
-  <si>
-    <t>FA-11476</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>FA-11398</t>
-  </si>
-  <si>
-    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
-  </si>
-  <si>
-    <t>FA-11399</t>
-  </si>
-  <si>
-    <t>FA-11492</t>
-  </si>
-  <si>
-    <t>ROSSILY PEREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11523</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11502</t>
-  </si>
-  <si>
-    <t>WESCLY JEAN DE MEDEIROS</t>
-  </si>
-  <si>
-    <t>FA-11473</t>
-  </si>
-  <si>
-    <t>FA-11278</t>
-  </si>
-  <si>
-    <t>FELIPE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11432</t>
-  </si>
-  <si>
-    <t>RAYANE ROBERTA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11475</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
-    <t>FA-11478</t>
-  </si>
-  <si>
-    <t>FA-11558</t>
-  </si>
-  <si>
-    <t>FA-11472</t>
-  </si>
-  <si>
-    <t>FA-11327</t>
-  </si>
-  <si>
-    <t>MAICON LOPES SILVA</t>
-  </si>
-  <si>
-    <t>FA-11267</t>
-  </si>
-  <si>
-    <t>ANNY KATARINA ACIOLE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11599</t>
-  </si>
-  <si>
-    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>FA-11575</t>
-  </si>
-  <si>
-    <t>ADRIANO TEOTONIO DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11589</t>
-  </si>
-  <si>
-    <t>FA-11453</t>
-  </si>
-  <si>
-    <t>FA-11400</t>
-  </si>
-  <si>
-    <t>FA-11474</t>
-  </si>
-  <si>
-    <t>FA-11525</t>
-  </si>
-  <si>
-    <t>FA-11481</t>
-  </si>
-  <si>
-    <t>FA-11559</t>
-  </si>
-  <si>
-    <t>FA-11560</t>
-  </si>
-  <si>
-    <t>FA-11493</t>
-  </si>
-  <si>
-    <t>FA-11526</t>
-  </si>
-  <si>
-    <t>FA-11401</t>
-  </si>
-  <si>
-    <t>FA-11402</t>
-  </si>
-  <si>
-    <t>FA-11279</t>
-  </si>
-  <si>
-    <t>FA-11503</t>
-  </si>
-  <si>
-    <t>FA-11482</t>
-  </si>
-  <si>
-    <t>FA-11433</t>
-  </si>
-  <si>
-    <t>FA-11411</t>
-  </si>
-  <si>
-    <t>FA-11483</t>
-  </si>
-  <si>
-    <t>FA-11484</t>
-  </si>
-  <si>
-    <t>FA-11561</t>
-  </si>
-  <si>
-    <t>FA-11268</t>
-  </si>
-  <si>
-    <t>FA-11328</t>
-  </si>
-  <si>
-    <t>FA-11479</t>
-  </si>
-  <si>
-    <t>FA-11600</t>
-  </si>
-  <si>
-    <t>FA-11590</t>
-  </si>
-  <si>
-    <t>FA-11577</t>
-  </si>
-  <si>
-    <t>FA-11480</t>
-  </si>
-  <si>
-    <t>FA-11562</t>
-  </si>
-  <si>
-    <t>FA-11563</t>
-  </si>
-  <si>
-    <t>FA-11487</t>
-  </si>
-  <si>
-    <t>FA-11494</t>
-  </si>
-  <si>
-    <t>FA-11488</t>
-  </si>
-  <si>
-    <t>FA-11504</t>
-  </si>
-  <si>
-    <t>FA-11280</t>
-  </si>
-  <si>
-    <t>FA-11434</t>
-  </si>
-  <si>
-    <t>FA-11412</t>
-  </si>
-  <si>
-    <t>FA-11489</t>
-  </si>
-  <si>
-    <t>FA-11491</t>
-  </si>
-  <si>
-    <t>FA-11564</t>
-  </si>
-  <si>
-    <t>FA-11329</t>
-  </si>
-  <si>
-    <t>FA-11601</t>
-  </si>
-  <si>
-    <t>FA-11591</t>
-  </si>
-  <si>
-    <t>FA-11578</t>
   </si>
 </sst>
 </file>
@@ -702,7 +705,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S115"/>
+  <dimension ref="A1:S116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.13657760620117" customWidth="1" style="1"/>
@@ -819,10 +822,10 @@
         <v>23</v>
       </c>
       <c r="F6" s="8">
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="G6" s="8">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>24</v>
@@ -878,10 +881,10 @@
         <v>23</v>
       </c>
       <c r="F7" s="8">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="G7" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>25</v>
@@ -937,10 +940,10 @@
         <v>23</v>
       </c>
       <c r="F8" s="8">
-        <v>-38</v>
+        <v>-39</v>
       </c>
       <c r="G8" s="8">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>24</v>
@@ -996,10 +999,10 @@
         <v>23</v>
       </c>
       <c r="F9" s="8">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="G9" s="8">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>25</v>
@@ -1055,10 +1058,10 @@
         <v>46127</v>
       </c>
       <c r="F10" s="8">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="G10" s="8">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>25</v>
@@ -1114,10 +1117,10 @@
         <v>46097</v>
       </c>
       <c r="F11" s="8">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="G11" s="8">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>25</v>
@@ -1173,10 +1176,10 @@
         <v>23</v>
       </c>
       <c r="F12" s="8">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="G12" s="8">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>25</v>
@@ -1232,10 +1235,10 @@
         <v>46141</v>
       </c>
       <c r="F13" s="8">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="G13" s="8">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>25</v>
@@ -1291,10 +1294,10 @@
         <v>46122</v>
       </c>
       <c r="F14" s="8">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="G14" s="8">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>25</v>
@@ -1350,10 +1353,10 @@
         <v>23</v>
       </c>
       <c r="F15" s="8">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="G15" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>25</v>
@@ -1409,10 +1412,10 @@
         <v>23</v>
       </c>
       <c r="F16" s="8">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="G16" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>25</v>
@@ -1427,7 +1430,7 @@
         <v>23</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>23</v>
@@ -1448,7 +1451,7 @@
         <v>33</v>
       </c>
       <c r="S16" s="9">
-        <v>350</v>
+        <v>408.24</v>
       </c>
     </row>
     <row r="17" ht="23" customHeight="1">
@@ -1456,22 +1459,22 @@
         <v>22</v>
       </c>
       <c r="B17" s="7">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="C17" s="7">
-        <v>46125</v>
+        <v>45930</v>
       </c>
       <c r="D17" s="7">
-        <v>46125</v>
+        <v>46142</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F17" s="8">
-        <v>-24</v>
+        <v>-8</v>
       </c>
       <c r="G17" s="8">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>25</v>
@@ -1480,13 +1483,13 @@
         <v>25</v>
       </c>
       <c r="J17" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L17" s="6" t="s">
         <v>47</v>
-      </c>
-      <c r="K17" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L17" s="6" t="s">
-        <v>32</v>
       </c>
       <c r="M17" s="6" t="s">
         <v>23</v>
@@ -1504,10 +1507,10 @@
         <v>23</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="S17" s="9">
-        <v>408.24</v>
+        <v>185.5</v>
       </c>
     </row>
     <row r="18" ht="23" customHeight="1">
@@ -1515,43 +1518,43 @@
         <v>22</v>
       </c>
       <c r="B18" s="7">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="C18" s="7">
-        <v>45930</v>
+        <v>46113</v>
       </c>
       <c r="D18" s="7">
-        <v>46142</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>23</v>
+        <v>46150</v>
+      </c>
+      <c r="E18" s="7">
+        <v>46141</v>
       </c>
       <c r="F18" s="8">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="G18" s="8">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I18" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M18" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>28</v>
@@ -1560,13 +1563,13 @@
         <v>23</v>
       </c>
       <c r="Q18" s="6" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="S18" s="9">
-        <v>185.5</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="19" ht="23" customHeight="1">
@@ -1577,40 +1580,40 @@
         <v>46146</v>
       </c>
       <c r="C19" s="7">
-        <v>46113</v>
+        <v>46132</v>
       </c>
       <c r="D19" s="7">
-        <v>46150</v>
-      </c>
-      <c r="E19" s="7">
-        <v>46141</v>
+        <v>46132</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F19" s="8">
-        <v>1</v>
+        <v>-18</v>
       </c>
       <c r="G19" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K19" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>28</v>
@@ -1619,13 +1622,13 @@
         <v>23</v>
       </c>
       <c r="Q19" s="6" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="S19" s="9">
-        <v>12.9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" ht="23" customHeight="1">
@@ -1636,40 +1639,40 @@
         <v>46146</v>
       </c>
       <c r="C20" s="7">
-        <v>46132</v>
+        <v>46153</v>
       </c>
       <c r="D20" s="7">
-        <v>46132</v>
+        <v>46153</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F20" s="8">
-        <v>-17</v>
+        <v>3</v>
       </c>
       <c r="G20" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>28</v>
@@ -1684,7 +1687,7 @@
         <v>30</v>
       </c>
       <c r="S20" s="9">
-        <v>50</v>
+        <v>61.21</v>
       </c>
     </row>
     <row r="21" ht="23" customHeight="1">
@@ -1695,40 +1698,40 @@
         <v>46146</v>
       </c>
       <c r="C21" s="7">
-        <v>46153</v>
+        <v>46125</v>
       </c>
       <c r="D21" s="7">
-        <v>46153</v>
+        <v>46125</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F21" s="8">
-        <v>4</v>
+        <v>-25</v>
       </c>
       <c r="G21" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I21" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>28</v>
@@ -1743,7 +1746,7 @@
         <v>30</v>
       </c>
       <c r="S21" s="9">
-        <v>61.21</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" ht="23" customHeight="1">
@@ -1754,19 +1757,19 @@
         <v>46146</v>
       </c>
       <c r="C22" s="7">
-        <v>46125</v>
+        <v>46082</v>
       </c>
       <c r="D22" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>23</v>
+        <v>46146</v>
+      </c>
+      <c r="E22" s="7">
+        <v>46097</v>
       </c>
       <c r="F22" s="8">
-        <v>-24</v>
+        <v>-4</v>
       </c>
       <c r="G22" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>25</v>
@@ -1775,13 +1778,13 @@
         <v>25</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="M22" s="6" t="s">
         <v>23</v>
@@ -1796,13 +1799,13 @@
         <v>23</v>
       </c>
       <c r="Q22" s="6" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S22" s="9">
-        <v>80</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="23" ht="23" customHeight="1">
@@ -1813,19 +1816,19 @@
         <v>46146</v>
       </c>
       <c r="C23" s="7">
-        <v>46082</v>
+        <v>46139</v>
       </c>
       <c r="D23" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E23" s="7">
-        <v>46097</v>
+        <v>46139</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F23" s="8">
-        <v>-3</v>
+        <v>-11</v>
       </c>
       <c r="G23" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>25</v>
@@ -1834,13 +1837,13 @@
         <v>25</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="K23" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="M23" s="6" t="s">
         <v>23</v>
@@ -1852,16 +1855,16 @@
         <v>28</v>
       </c>
       <c r="P23" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q23" s="6" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S23" s="9">
-        <v>146.55</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" ht="23" customHeight="1">
@@ -1881,10 +1884,10 @@
         <v>23</v>
       </c>
       <c r="F24" s="8">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="G24" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>25</v>
@@ -1893,16 +1896,16 @@
         <v>25</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="N24" s="6" t="s">
         <v>28</v>
@@ -1911,7 +1914,7 @@
         <v>28</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q24" s="6" t="s">
         <v>23</v>
@@ -1920,7 +1923,7 @@
         <v>30</v>
       </c>
       <c r="S24" s="9">
-        <v>150</v>
+        <v>204.67</v>
       </c>
     </row>
     <row r="25" ht="23" customHeight="1">
@@ -1931,19 +1934,19 @@
         <v>46146</v>
       </c>
       <c r="C25" s="7">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="D25" s="7">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F25" s="8">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="G25" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>25</v>
@@ -1952,16 +1955,16 @@
         <v>25</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K25" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="N25" s="6" t="s">
         <v>28</v>
@@ -1979,7 +1982,7 @@
         <v>30</v>
       </c>
       <c r="S25" s="9">
-        <v>204.67</v>
+        <v>205.82</v>
       </c>
     </row>
     <row r="26" ht="23" customHeight="1">
@@ -1990,19 +1993,19 @@
         <v>46146</v>
       </c>
       <c r="C26" s="7">
-        <v>46146</v>
+        <v>46139</v>
       </c>
       <c r="D26" s="7">
-        <v>46146</v>
+        <v>46139</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F26" s="8">
-        <v>-3</v>
+        <v>-11</v>
       </c>
       <c r="G26" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>25</v>
@@ -2011,16 +2014,16 @@
         <v>25</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K26" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="N26" s="6" t="s">
         <v>28</v>
@@ -2038,7 +2041,7 @@
         <v>30</v>
       </c>
       <c r="S26" s="9">
-        <v>205.82</v>
+        <v>350</v>
       </c>
     </row>
     <row r="27" ht="23" customHeight="1">
@@ -2049,37 +2052,37 @@
         <v>46146</v>
       </c>
       <c r="C27" s="7">
-        <v>46139</v>
+        <v>45901</v>
       </c>
       <c r="D27" s="7">
-        <v>46139</v>
+        <v>45938</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F27" s="8">
-        <v>-10</v>
+        <v>-212</v>
       </c>
       <c r="G27" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="I27" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K27" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="N27" s="6" t="s">
         <v>28</v>
@@ -2097,7 +2100,7 @@
         <v>30</v>
       </c>
       <c r="S27" s="9">
-        <v>350</v>
+        <v>363</v>
       </c>
     </row>
     <row r="28" ht="23" customHeight="1">
@@ -2108,37 +2111,37 @@
         <v>46146</v>
       </c>
       <c r="C28" s="7">
-        <v>45901</v>
+        <v>46146</v>
       </c>
       <c r="D28" s="7">
-        <v>45938</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>23</v>
+        <v>46146</v>
+      </c>
+      <c r="E28" s="7">
+        <v>46119</v>
       </c>
       <c r="F28" s="8">
-        <v>-211</v>
+        <v>-4</v>
       </c>
       <c r="G28" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="I28" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="N28" s="6" t="s">
         <v>28</v>
@@ -2150,13 +2153,13 @@
         <v>23</v>
       </c>
       <c r="Q28" s="6" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="R28" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S28" s="9">
-        <v>363</v>
+        <v>600</v>
       </c>
     </row>
     <row r="29" ht="23" customHeight="1">
@@ -2173,13 +2176,13 @@
         <v>46146</v>
       </c>
       <c r="E29" s="7">
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="F29" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G29" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>25</v>
@@ -2188,16 +2191,16 @@
         <v>25</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="N29" s="6" t="s">
         <v>28</v>
@@ -2215,7 +2218,7 @@
         <v>30</v>
       </c>
       <c r="S29" s="9">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="30" ht="23" customHeight="1">
@@ -2235,10 +2238,10 @@
         <v>46141</v>
       </c>
       <c r="F30" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G30" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>25</v>
@@ -2247,16 +2250,16 @@
         <v>25</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="N30" s="6" t="s">
         <v>28</v>
@@ -2291,13 +2294,13 @@
         <v>46146</v>
       </c>
       <c r="E31" s="7">
-        <v>46141</v>
+        <v>46112</v>
       </c>
       <c r="F31" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G31" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>25</v>
@@ -2306,13 +2309,13 @@
         <v>25</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="M31" s="6" t="s">
         <v>23</v>
@@ -2333,7 +2336,7 @@
         <v>30</v>
       </c>
       <c r="S31" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="32" ht="23" customHeight="1">
@@ -2350,13 +2353,13 @@
         <v>46146</v>
       </c>
       <c r="E32" s="7">
-        <v>46100</v>
+        <v>46119</v>
       </c>
       <c r="F32" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G32" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>25</v>
@@ -2365,16 +2368,16 @@
         <v>25</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="N32" s="6" t="s">
         <v>28</v>
@@ -2392,7 +2395,7 @@
         <v>30</v>
       </c>
       <c r="S32" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="33" ht="23" customHeight="1">
@@ -2403,19 +2406,19 @@
         <v>46146</v>
       </c>
       <c r="C33" s="7">
-        <v>46146</v>
+        <v>46132</v>
       </c>
       <c r="D33" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E33" s="7">
-        <v>46112</v>
+        <v>46132</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F33" s="8">
-        <v>-3</v>
+        <v>-18</v>
       </c>
       <c r="G33" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>25</v>
@@ -2424,13 +2427,13 @@
         <v>25</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="M33" s="6" t="s">
         <v>23</v>
@@ -2445,13 +2448,13 @@
         <v>23</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R33" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S33" s="9">
-        <v>630</v>
+        <v>655.21</v>
       </c>
     </row>
     <row r="34" ht="23" customHeight="1">
@@ -2468,13 +2471,13 @@
         <v>46146</v>
       </c>
       <c r="E34" s="7">
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="F34" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G34" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>25</v>
@@ -2483,16 +2486,16 @@
         <v>25</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>28</v>
@@ -2507,10 +2510,10 @@
         <v>39</v>
       </c>
       <c r="R34" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S34" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="35" ht="23" customHeight="1">
@@ -2521,19 +2524,19 @@
         <v>46146</v>
       </c>
       <c r="C35" s="7">
-        <v>46132</v>
+        <v>46146</v>
       </c>
       <c r="D35" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>23</v>
+        <v>46146</v>
+      </c>
+      <c r="E35" s="7">
+        <v>46119</v>
       </c>
       <c r="F35" s="8">
-        <v>-17</v>
+        <v>-4</v>
       </c>
       <c r="G35" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>25</v>
@@ -2542,13 +2545,13 @@
         <v>25</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>23</v>
@@ -2560,16 +2563,16 @@
         <v>28</v>
       </c>
       <c r="P35" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q35" s="6" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="R35" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S35" s="9">
-        <v>655.21</v>
+        <v>700</v>
       </c>
     </row>
     <row r="36" ht="23" customHeight="1">
@@ -2577,19 +2580,19 @@
         <v>22</v>
       </c>
       <c r="B36" s="7">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="C36" s="7">
-        <v>46146</v>
+        <v>46139</v>
       </c>
       <c r="D36" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E36" s="7">
-        <v>46141</v>
+        <v>46139</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F36" s="8">
-        <v>-3</v>
+        <v>-11</v>
       </c>
       <c r="G36" s="8">
         <v>-3</v>
@@ -2601,13 +2604,13 @@
         <v>25</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>23</v>
@@ -2622,13 +2625,13 @@
         <v>23</v>
       </c>
       <c r="Q36" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R36" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S36" s="9">
-        <v>680</v>
+        <v>103.36</v>
       </c>
     </row>
     <row r="37" ht="23" customHeight="1">
@@ -2636,7 +2639,7 @@
         <v>22</v>
       </c>
       <c r="B37" s="7">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="C37" s="7">
         <v>46146</v>
@@ -2644,11 +2647,11 @@
       <c r="D37" s="7">
         <v>46146</v>
       </c>
-      <c r="E37" s="7">
-        <v>46119</v>
+      <c r="E37" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F37" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G37" s="8">
         <v>-3</v>
@@ -2660,13 +2663,13 @@
         <v>25</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>23</v>
@@ -2678,16 +2681,16 @@
         <v>28</v>
       </c>
       <c r="P37" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q37" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R37" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S37" s="9">
-        <v>700</v>
+        <v>124.27</v>
       </c>
     </row>
     <row r="38" ht="23" customHeight="1">
@@ -2695,22 +2698,22 @@
         <v>22</v>
       </c>
       <c r="B38" s="7">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="C38" s="7">
-        <v>46132</v>
+        <v>46146</v>
       </c>
       <c r="D38" s="7">
-        <v>46132</v>
+        <v>46146</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F38" s="8">
-        <v>-17</v>
+        <v>-4</v>
       </c>
       <c r="G38" s="8">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>25</v>
@@ -2719,13 +2722,13 @@
         <v>25</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>23</v>
@@ -2746,7 +2749,7 @@
         <v>30</v>
       </c>
       <c r="S38" s="9">
-        <v>3.82</v>
+        <v>380</v>
       </c>
     </row>
     <row r="39" ht="23" customHeight="1">
@@ -2754,22 +2757,22 @@
         <v>22</v>
       </c>
       <c r="B39" s="7">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="C39" s="7">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="D39" s="7">
-        <v>46139</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>23</v>
+        <v>46142</v>
+      </c>
+      <c r="E39" s="7">
+        <v>46148</v>
       </c>
       <c r="F39" s="8">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="G39" s="8">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>25</v>
@@ -2778,13 +2781,13 @@
         <v>25</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="M39" s="6" t="s">
         <v>23</v>
@@ -2799,13 +2802,13 @@
         <v>23</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="S39" s="9">
-        <v>103.36</v>
+        <v>685.71</v>
       </c>
     </row>
     <row r="40" ht="23" customHeight="1">
@@ -2813,37 +2816,37 @@
         <v>22</v>
       </c>
       <c r="B40" s="7">
-        <v>46147</v>
+        <v>46150</v>
       </c>
       <c r="C40" s="7">
-        <v>46146</v>
+        <v>46125</v>
       </c>
       <c r="D40" s="7">
-        <v>46146</v>
+        <v>46125</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F40" s="8">
-        <v>-3</v>
+        <v>-25</v>
       </c>
       <c r="G40" s="8">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>25</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="M40" s="6" t="s">
         <v>23</v>
@@ -2852,7 +2855,7 @@
         <v>28</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>23</v>
@@ -2864,7 +2867,7 @@
         <v>30</v>
       </c>
       <c r="S40" s="9">
-        <v>124.27</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="41" ht="23" customHeight="1">
@@ -2872,37 +2875,37 @@
         <v>22</v>
       </c>
       <c r="B41" s="7">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="C41" s="7">
-        <v>46125</v>
+        <v>46146</v>
       </c>
       <c r="D41" s="7">
-        <v>46125</v>
+        <v>46146</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F41" s="8">
-        <v>-24</v>
+        <v>-4</v>
       </c>
       <c r="G41" s="8">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>25</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="M41" s="6" t="s">
         <v>23</v>
@@ -2911,7 +2914,7 @@
         <v>28</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="P41" s="6" t="s">
         <v>23</v>
@@ -2923,7 +2926,7 @@
         <v>30</v>
       </c>
       <c r="S41" s="9">
-        <v>150</v>
+        <v>170</v>
       </c>
     </row>
     <row r="42" ht="23" customHeight="1">
@@ -2931,19 +2934,19 @@
         <v>22</v>
       </c>
       <c r="B42" s="7">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="C42" s="7">
-        <v>46142</v>
+        <v>46125</v>
       </c>
       <c r="D42" s="7">
-        <v>46142</v>
-      </c>
-      <c r="E42" s="7">
-        <v>46148</v>
+        <v>46125</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F42" s="8">
-        <v>-7</v>
+        <v>-25</v>
       </c>
       <c r="G42" s="8">
         <v>0</v>
@@ -2955,13 +2958,13 @@
         <v>23</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="M42" s="6" t="s">
         <v>23</v>
@@ -2970,19 +2973,19 @@
         <v>28</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q42" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R42" s="6" t="s">
-        <v>89</v>
+        <v>33</v>
       </c>
       <c r="S42" s="9">
-        <v>685.71</v>
+        <v>250</v>
       </c>
     </row>
     <row r="43" ht="23" customHeight="1">
@@ -2990,22 +2993,22 @@
         <v>22</v>
       </c>
       <c r="B43" s="7">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="C43" s="7">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="D43" s="7">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="E43" s="7">
-        <v>46149</v>
+        <v>46097</v>
       </c>
       <c r="F43" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G43" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H43" s="6" t="s">
         <v>23</v>
@@ -3014,34 +3017,34 @@
         <v>23</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>90</v>
+        <v>31</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>91</v>
+        <v>32</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>91</v>
+        <v>23</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P43" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q43" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S43" s="9">
-        <v>2100</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="44" ht="23" customHeight="1">
@@ -3049,22 +3052,22 @@
         <v>22</v>
       </c>
       <c r="B44" s="7">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="C44" s="7">
-        <v>46113</v>
+        <v>46153</v>
       </c>
       <c r="D44" s="7">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="E44" s="7">
-        <v>46149</v>
+        <v>46112</v>
       </c>
       <c r="F44" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G44" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>23</v>
@@ -3073,22 +3076,22 @@
         <v>23</v>
       </c>
       <c r="J44" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L44" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="K44" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L44" s="6" t="s">
-        <v>93</v>
-      </c>
       <c r="M44" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>23</v>
@@ -3100,7 +3103,7 @@
         <v>30</v>
       </c>
       <c r="S44" s="9">
-        <v>2100</v>
+        <v>600</v>
       </c>
     </row>
     <row r="45" ht="23" customHeight="1">
@@ -3108,22 +3111,22 @@
         <v>22</v>
       </c>
       <c r="B45" s="7">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="C45" s="7">
-        <v>46113</v>
+        <v>46153</v>
       </c>
       <c r="D45" s="7">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="E45" s="7">
-        <v>46149</v>
+        <v>46119</v>
       </c>
       <c r="F45" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G45" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H45" s="6" t="s">
         <v>23</v>
@@ -3132,22 +3135,22 @@
         <v>23</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K45" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="N45" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P45" s="6" t="s">
         <v>23</v>
@@ -3159,7 +3162,7 @@
         <v>30</v>
       </c>
       <c r="S45" s="9">
-        <v>4400</v>
+        <v>600</v>
       </c>
     </row>
     <row r="46" ht="23" customHeight="1">
@@ -3170,19 +3173,19 @@
         <v>46153</v>
       </c>
       <c r="C46" s="7">
-        <v>46082</v>
+        <v>46153</v>
       </c>
       <c r="D46" s="7">
         <v>46153</v>
       </c>
       <c r="E46" s="7">
-        <v>46097</v>
+        <v>46127</v>
       </c>
       <c r="F46" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G46" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>23</v>
@@ -3191,34 +3194,34 @@
         <v>23</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q46" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R46" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S46" s="9">
-        <v>146.55</v>
+        <v>600</v>
       </c>
     </row>
     <row r="47" ht="23" customHeight="1">
@@ -3235,13 +3238,13 @@
         <v>46153</v>
       </c>
       <c r="E47" s="7">
-        <v>46112</v>
+        <v>46141</v>
       </c>
       <c r="F47" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G47" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H47" s="6" t="s">
         <v>23</v>
@@ -3250,22 +3253,22 @@
         <v>23</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K47" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>98</v>
+        <v>23</v>
       </c>
       <c r="N47" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P47" s="6" t="s">
         <v>23</v>
@@ -3277,7 +3280,7 @@
         <v>30</v>
       </c>
       <c r="S47" s="9">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="48" ht="23" customHeight="1">
@@ -3294,13 +3297,13 @@
         <v>46153</v>
       </c>
       <c r="E48" s="7">
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="F48" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G48" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>23</v>
@@ -3309,22 +3312,22 @@
         <v>23</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="K48" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>23</v>
@@ -3336,7 +3339,7 @@
         <v>30</v>
       </c>
       <c r="S48" s="9">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="49" ht="23" customHeight="1">
@@ -3353,13 +3356,13 @@
         <v>46153</v>
       </c>
       <c r="E49" s="7">
-        <v>46127</v>
+        <v>46119</v>
       </c>
       <c r="F49" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G49" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H49" s="6" t="s">
         <v>23</v>
@@ -3368,22 +3371,22 @@
         <v>23</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N49" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O49" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P49" s="6" t="s">
         <v>23</v>
@@ -3392,10 +3395,10 @@
         <v>39</v>
       </c>
       <c r="R49" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S49" s="9">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="50" ht="23" customHeight="1">
@@ -3412,13 +3415,13 @@
         <v>46153</v>
       </c>
       <c r="E50" s="7">
-        <v>46141</v>
+        <v>46112</v>
       </c>
       <c r="F50" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G50" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H50" s="6" t="s">
         <v>23</v>
@@ -3427,22 +3430,22 @@
         <v>23</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="M50" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>23</v>
@@ -3454,7 +3457,7 @@
         <v>30</v>
       </c>
       <c r="S50" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="51" ht="23" customHeight="1">
@@ -3471,13 +3474,13 @@
         <v>46153</v>
       </c>
       <c r="E51" s="7">
-        <v>46141</v>
+        <v>46112</v>
       </c>
       <c r="F51" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G51" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H51" s="6" t="s">
         <v>23</v>
@@ -3486,22 +3489,22 @@
         <v>23</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K51" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="M51" s="6" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="N51" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O51" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P51" s="6" t="s">
         <v>23</v>
@@ -3513,7 +3516,7 @@
         <v>30</v>
       </c>
       <c r="S51" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="52" ht="23" customHeight="1">
@@ -3533,10 +3536,10 @@
         <v>46119</v>
       </c>
       <c r="F52" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G52" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>23</v>
@@ -3545,34 +3548,34 @@
         <v>23</v>
       </c>
       <c r="J52" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="K52" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L52" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="K52" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L52" s="6" t="s">
-        <v>105</v>
-      </c>
       <c r="M52" s="6" t="s">
-        <v>105</v>
+        <v>23</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q52" s="6" t="s">
         <v>39</v>
       </c>
       <c r="R52" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S52" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="53" ht="23" customHeight="1">
@@ -3589,13 +3592,13 @@
         <v>46153</v>
       </c>
       <c r="E53" s="7">
-        <v>46112</v>
+        <v>46127</v>
       </c>
       <c r="F53" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G53" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H53" s="6" t="s">
         <v>23</v>
@@ -3604,22 +3607,22 @@
         <v>23</v>
       </c>
       <c r="J53" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="K53" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L53" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="K53" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L53" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="M53" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N53" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O53" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P53" s="6" t="s">
         <v>23</v>
@@ -3648,13 +3651,13 @@
         <v>46153</v>
       </c>
       <c r="E54" s="7">
-        <v>46112</v>
+        <v>46150</v>
       </c>
       <c r="F54" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G54" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H54" s="6" t="s">
         <v>23</v>
@@ -3663,22 +3666,22 @@
         <v>23</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>37</v>
+        <v>83</v>
       </c>
       <c r="M54" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>23</v>
@@ -3707,13 +3710,13 @@
         <v>46153</v>
       </c>
       <c r="E55" s="7">
-        <v>46119</v>
+        <v>46127</v>
       </c>
       <c r="F55" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G55" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H55" s="6" t="s">
         <v>23</v>
@@ -3722,25 +3725,25 @@
         <v>23</v>
       </c>
       <c r="J55" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="K55" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L55" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="K55" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L55" s="6" t="s">
-        <v>110</v>
-      </c>
       <c r="M55" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N55" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O55" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P55" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q55" s="6" t="s">
         <v>39</v>
@@ -3749,7 +3752,7 @@
         <v>30</v>
       </c>
       <c r="S55" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="56" ht="23" customHeight="1">
@@ -3766,13 +3769,13 @@
         <v>46153</v>
       </c>
       <c r="E56" s="7">
-        <v>46127</v>
+        <v>46119</v>
       </c>
       <c r="F56" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G56" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H56" s="6" t="s">
         <v>23</v>
@@ -3781,22 +3784,22 @@
         <v>23</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K56" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>112</v>
+        <v>61</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>23</v>
@@ -3808,7 +3811,7 @@
         <v>30</v>
       </c>
       <c r="S56" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="57" ht="23" customHeight="1">
@@ -3825,13 +3828,13 @@
         <v>46153</v>
       </c>
       <c r="E57" s="7">
-        <v>46127</v>
+        <v>46092</v>
       </c>
       <c r="F57" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G57" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H57" s="6" t="s">
         <v>23</v>
@@ -3840,22 +3843,22 @@
         <v>23</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K57" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="M57" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N57" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O57" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P57" s="6" t="s">
         <v>23</v>
@@ -3887,10 +3890,10 @@
         <v>46119</v>
       </c>
       <c r="F58" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G58" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H58" s="6" t="s">
         <v>23</v>
@@ -3899,22 +3902,22 @@
         <v>23</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="K58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>23</v>
@@ -3926,7 +3929,7 @@
         <v>30</v>
       </c>
       <c r="S58" s="9">
-        <v>650</v>
+        <v>670</v>
       </c>
     </row>
     <row r="59" ht="23" customHeight="1">
@@ -3943,13 +3946,13 @@
         <v>46153</v>
       </c>
       <c r="E59" s="7">
-        <v>46092</v>
+        <v>46119</v>
       </c>
       <c r="F59" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G59" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H59" s="6" t="s">
         <v>23</v>
@@ -3958,22 +3961,22 @@
         <v>23</v>
       </c>
       <c r="J59" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K59" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L59" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="K59" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L59" s="6" t="s">
-        <v>117</v>
-      </c>
       <c r="M59" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N59" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O59" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P59" s="6" t="s">
         <v>23</v>
@@ -3985,7 +3988,7 @@
         <v>30</v>
       </c>
       <c r="S59" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="60" ht="23" customHeight="1">
@@ -4005,10 +4008,10 @@
         <v>46119</v>
       </c>
       <c r="F60" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G60" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H60" s="6" t="s">
         <v>23</v>
@@ -4017,22 +4020,22 @@
         <v>23</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>119</v>
+        <v>32</v>
       </c>
       <c r="M60" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>23</v>
@@ -4041,10 +4044,10 @@
         <v>39</v>
       </c>
       <c r="R60" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S60" s="9">
-        <v>670</v>
+        <v>680</v>
       </c>
     </row>
     <row r="61" ht="23" customHeight="1">
@@ -4061,13 +4064,13 @@
         <v>46153</v>
       </c>
       <c r="E61" s="7">
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="F61" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G61" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H61" s="6" t="s">
         <v>23</v>
@@ -4076,22 +4079,22 @@
         <v>23</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="M61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N61" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P61" s="6" t="s">
         <v>23</v>
@@ -4100,7 +4103,7 @@
         <v>39</v>
       </c>
       <c r="R61" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S61" s="9">
         <v>680</v>
@@ -4123,10 +4126,10 @@
         <v>46119</v>
       </c>
       <c r="F62" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G62" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H62" s="6" t="s">
         <v>23</v>
@@ -4135,34 +4138,34 @@
         <v>23</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="M62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q62" s="6" t="s">
         <v>39</v>
       </c>
       <c r="R62" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S62" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="63" ht="23" customHeight="1">
@@ -4179,13 +4182,13 @@
         <v>46153</v>
       </c>
       <c r="E63" s="7">
-        <v>46141</v>
+        <v>46099</v>
       </c>
       <c r="F63" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G63" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H63" s="6" t="s">
         <v>23</v>
@@ -4194,22 +4197,22 @@
         <v>23</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="K63" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="M63" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N63" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P63" s="6" t="s">
         <v>23</v>
@@ -4221,7 +4224,7 @@
         <v>33</v>
       </c>
       <c r="S63" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="64" ht="23" customHeight="1">
@@ -4238,13 +4241,13 @@
         <v>46153</v>
       </c>
       <c r="E64" s="7">
-        <v>46119</v>
+        <v>46092</v>
       </c>
       <c r="F64" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G64" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H64" s="6" t="s">
         <v>23</v>
@@ -4253,25 +4256,25 @@
         <v>23</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K64" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>59</v>
+        <v>123</v>
       </c>
       <c r="M64" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q64" s="6" t="s">
         <v>39</v>
@@ -4297,13 +4300,13 @@
         <v>46153</v>
       </c>
       <c r="E65" s="7">
-        <v>46099</v>
+        <v>46148</v>
       </c>
       <c r="F65" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G65" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H65" s="6" t="s">
         <v>23</v>
@@ -4312,34 +4315,34 @@
         <v>23</v>
       </c>
       <c r="J65" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="K65" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L65" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="K65" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L65" s="6" t="s">
-        <v>126</v>
-      </c>
       <c r="M65" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N65" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="O65" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="P65" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q65" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R65" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="O65" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="P65" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q65" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R65" s="6" t="s">
-        <v>33</v>
-      </c>
       <c r="S65" s="9">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="66" ht="23" customHeight="1">
@@ -4350,43 +4353,43 @@
         <v>46153</v>
       </c>
       <c r="C66" s="7">
-        <v>46153</v>
+        <v>46147</v>
       </c>
       <c r="D66" s="7">
-        <v>46153</v>
+        <v>46147</v>
       </c>
       <c r="E66" s="7">
-        <v>46092</v>
+        <v>46148</v>
       </c>
       <c r="F66" s="8">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="G66" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I66" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J66" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="K66" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L66" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="K66" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L66" s="6" t="s">
-        <v>128</v>
-      </c>
       <c r="M66" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>23</v>
@@ -4395,10 +4398,10 @@
         <v>39</v>
       </c>
       <c r="R66" s="6" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="S66" s="9">
-        <v>700</v>
+        <v>1028.57</v>
       </c>
     </row>
     <row r="67" ht="23" customHeight="1">
@@ -4406,58 +4409,58 @@
         <v>22</v>
       </c>
       <c r="B67" s="7">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C67" s="7">
-        <v>46153</v>
+        <v>46132</v>
       </c>
       <c r="D67" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E67" s="7">
-        <v>46148</v>
+        <v>46132</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F67" s="8">
-        <v>4</v>
+        <v>-18</v>
       </c>
       <c r="G67" s="8">
         <v>4</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I67" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K67" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>130</v>
+        <v>61</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="N67" s="6" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="O67" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P67" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q67" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R67" s="6" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="S67" s="9">
-        <v>800</v>
+        <v>317.54</v>
       </c>
     </row>
     <row r="68" ht="23" customHeight="1">
@@ -4465,58 +4468,58 @@
         <v>22</v>
       </c>
       <c r="B68" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C68" s="7">
-        <v>46147</v>
+        <v>46082</v>
       </c>
       <c r="D68" s="7">
-        <v>46147</v>
+        <v>46160</v>
       </c>
       <c r="E68" s="7">
-        <v>46148</v>
+        <v>46097</v>
       </c>
       <c r="F68" s="8">
-        <v>-2</v>
+        <v>10</v>
       </c>
       <c r="G68" s="8">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I68" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J68" s="6" t="s">
-        <v>131</v>
+        <v>31</v>
       </c>
       <c r="K68" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L68" s="6" t="s">
-        <v>132</v>
+        <v>32</v>
       </c>
       <c r="M68" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q68" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R68" s="6" t="s">
-        <v>89</v>
+        <v>33</v>
       </c>
       <c r="S68" s="9">
-        <v>1028.57</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="69" ht="23" customHeight="1">
@@ -4524,22 +4527,22 @@
         <v>22</v>
       </c>
       <c r="B69" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C69" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="D69" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="E69" s="7">
-        <v>46148</v>
+        <v>46112</v>
       </c>
       <c r="F69" s="8">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G69" s="8">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H69" s="6" t="s">
         <v>23</v>
@@ -4548,22 +4551,22 @@
         <v>23</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="K69" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="M69" s="6" t="s">
-        <v>23</v>
+        <v>92</v>
       </c>
       <c r="N69" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O69" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P69" s="6" t="s">
         <v>23</v>
@@ -4572,10 +4575,10 @@
         <v>39</v>
       </c>
       <c r="R69" s="6" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="S69" s="9">
-        <v>1200</v>
+        <v>600</v>
       </c>
     </row>
     <row r="70" ht="23" customHeight="1">
@@ -4583,58 +4586,58 @@
         <v>22</v>
       </c>
       <c r="B70" s="7">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="C70" s="7">
-        <v>46132</v>
+        <v>46160</v>
       </c>
       <c r="D70" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E70" s="7" t="s">
-        <v>23</v>
+        <v>46160</v>
+      </c>
+      <c r="E70" s="7">
+        <v>46119</v>
       </c>
       <c r="F70" s="8">
-        <v>-17</v>
+        <v>10</v>
       </c>
       <c r="G70" s="8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I70" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="K70" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q70" s="6" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="R70" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S70" s="9">
-        <v>317.54</v>
+        <v>600</v>
       </c>
     </row>
     <row r="71" ht="23" customHeight="1">
@@ -4645,19 +4648,19 @@
         <v>46160</v>
       </c>
       <c r="C71" s="7">
-        <v>46082</v>
+        <v>46160</v>
       </c>
       <c r="D71" s="7">
         <v>46160</v>
       </c>
       <c r="E71" s="7">
-        <v>46097</v>
+        <v>46127</v>
       </c>
       <c r="F71" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G71" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H71" s="6" t="s">
         <v>23</v>
@@ -4666,34 +4669,34 @@
         <v>23</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>31</v>
+        <v>131</v>
       </c>
       <c r="K71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="M71" s="6" t="s">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="N71" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O71" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q71" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R71" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S71" s="9">
-        <v>146.55</v>
+        <v>600</v>
       </c>
     </row>
     <row r="72" ht="23" customHeight="1">
@@ -4710,13 +4713,13 @@
         <v>46160</v>
       </c>
       <c r="E72" s="7">
-        <v>46112</v>
+        <v>46119</v>
       </c>
       <c r="F72" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G72" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H72" s="6" t="s">
         <v>23</v>
@@ -4725,22 +4728,22 @@
         <v>23</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K72" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>23</v>
@@ -4749,10 +4752,10 @@
         <v>39</v>
       </c>
       <c r="R72" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S72" s="9">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="73" ht="23" customHeight="1">
@@ -4769,13 +4772,13 @@
         <v>46160</v>
       </c>
       <c r="E73" s="7">
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="F73" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G73" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H73" s="6" t="s">
         <v>23</v>
@@ -4784,22 +4787,22 @@
         <v>23</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="K73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="M73" s="6" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="N73" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O73" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P73" s="6" t="s">
         <v>23</v>
@@ -4811,7 +4814,7 @@
         <v>30</v>
       </c>
       <c r="S73" s="9">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="74" ht="23" customHeight="1">
@@ -4828,13 +4831,13 @@
         <v>46160</v>
       </c>
       <c r="E74" s="7">
-        <v>46127</v>
+        <v>46141</v>
       </c>
       <c r="F74" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G74" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H74" s="6" t="s">
         <v>23</v>
@@ -4843,22 +4846,22 @@
         <v>23</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>101</v>
+        <v>43</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>101</v>
+        <v>43</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>23</v>
@@ -4870,7 +4873,7 @@
         <v>30</v>
       </c>
       <c r="S74" s="9">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="75" ht="23" customHeight="1">
@@ -4890,10 +4893,10 @@
         <v>46119</v>
       </c>
       <c r="F75" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G75" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H75" s="6" t="s">
         <v>23</v>
@@ -4902,34 +4905,34 @@
         <v>23</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="K75" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M75" s="6" t="s">
-        <v>105</v>
+        <v>23</v>
       </c>
       <c r="N75" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O75" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P75" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q75" s="6" t="s">
         <v>39</v>
       </c>
       <c r="R75" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S75" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="76" ht="23" customHeight="1">
@@ -4946,13 +4949,13 @@
         <v>46160</v>
       </c>
       <c r="E76" s="7">
-        <v>46141</v>
+        <v>46127</v>
       </c>
       <c r="F76" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G76" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H76" s="6" t="s">
         <v>23</v>
@@ -4961,22 +4964,22 @@
         <v>23</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="M76" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>23</v>
@@ -4988,7 +4991,7 @@
         <v>30</v>
       </c>
       <c r="S76" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="77" ht="23" customHeight="1">
@@ -5005,13 +5008,13 @@
         <v>46160</v>
       </c>
       <c r="E77" s="7">
-        <v>46141</v>
+        <v>46112</v>
       </c>
       <c r="F77" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G77" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>23</v>
@@ -5020,22 +5023,22 @@
         <v>23</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="K77" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>43</v>
+        <v>101</v>
       </c>
       <c r="M77" s="6" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="N77" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O77" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P77" s="6" t="s">
         <v>23</v>
@@ -5047,7 +5050,7 @@
         <v>30</v>
       </c>
       <c r="S77" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="78" ht="23" customHeight="1">
@@ -5064,13 +5067,13 @@
         <v>46160</v>
       </c>
       <c r="E78" s="7">
-        <v>46119</v>
+        <v>46112</v>
       </c>
       <c r="F78" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G78" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H78" s="6" t="s">
         <v>23</v>
@@ -5079,25 +5082,25 @@
         <v>23</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L78" s="6" t="s">
-        <v>110</v>
+        <v>37</v>
       </c>
       <c r="M78" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q78" s="6" t="s">
         <v>39</v>
@@ -5123,13 +5126,13 @@
         <v>46160</v>
       </c>
       <c r="E79" s="7">
-        <v>46127</v>
+        <v>46150</v>
       </c>
       <c r="F79" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G79" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H79" s="6" t="s">
         <v>23</v>
@@ -5138,22 +5141,22 @@
         <v>23</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="M79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N79" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O79" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P79" s="6" t="s">
         <v>23</v>
@@ -5182,13 +5185,13 @@
         <v>46160</v>
       </c>
       <c r="E80" s="7">
-        <v>46112</v>
+        <v>46092</v>
       </c>
       <c r="F80" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G80" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H80" s="6" t="s">
         <v>23</v>
@@ -5197,22 +5200,22 @@
         <v>23</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L80" s="6" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="M80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>23</v>
@@ -5224,7 +5227,7 @@
         <v>30</v>
       </c>
       <c r="S80" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="81" ht="23" customHeight="1">
@@ -5241,13 +5244,13 @@
         <v>46160</v>
       </c>
       <c r="E81" s="7">
-        <v>46112</v>
+        <v>46127</v>
       </c>
       <c r="F81" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G81" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H81" s="6" t="s">
         <v>23</v>
@@ -5256,22 +5259,22 @@
         <v>23</v>
       </c>
       <c r="J81" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="M81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N81" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O81" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P81" s="6" t="s">
         <v>23</v>
@@ -5283,7 +5286,7 @@
         <v>30</v>
       </c>
       <c r="S81" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="82" ht="23" customHeight="1">
@@ -5300,13 +5303,13 @@
         <v>46160</v>
       </c>
       <c r="E82" s="7">
-        <v>46092</v>
+        <v>46119</v>
       </c>
       <c r="F82" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G82" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H82" s="6" t="s">
         <v>23</v>
@@ -5315,22 +5318,22 @@
         <v>23</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="K82" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>117</v>
+        <v>61</v>
       </c>
       <c r="M82" s="6" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>23</v>
@@ -5359,13 +5362,13 @@
         <v>46160</v>
       </c>
       <c r="E83" s="7">
-        <v>46127</v>
+        <v>46119</v>
       </c>
       <c r="F83" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G83" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H83" s="6" t="s">
         <v>23</v>
@@ -5374,7 +5377,7 @@
         <v>23</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="K83" s="6" t="s">
         <v>23</v>
@@ -5386,10 +5389,10 @@
         <v>23</v>
       </c>
       <c r="N83" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O83" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P83" s="6" t="s">
         <v>23</v>
@@ -5401,7 +5404,7 @@
         <v>30</v>
       </c>
       <c r="S83" s="9">
-        <v>650</v>
+        <v>670</v>
       </c>
     </row>
     <row r="84" ht="23" customHeight="1">
@@ -5418,13 +5421,13 @@
         <v>46160</v>
       </c>
       <c r="E84" s="7">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="F84" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G84" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H84" s="6" t="s">
         <v>23</v>
@@ -5433,22 +5436,22 @@
         <v>23</v>
       </c>
       <c r="J84" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="K84" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L84" s="6" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="M84" s="6" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>23</v>
@@ -5460,7 +5463,7 @@
         <v>30</v>
       </c>
       <c r="S84" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="85" ht="23" customHeight="1">
@@ -5480,10 +5483,10 @@
         <v>46119</v>
       </c>
       <c r="F85" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G85" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H85" s="6" t="s">
         <v>23</v>
@@ -5492,22 +5495,22 @@
         <v>23</v>
       </c>
       <c r="J85" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="K85" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L85" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M85" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N85" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O85" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P85" s="6" t="s">
         <v>23</v>
@@ -5519,7 +5522,7 @@
         <v>30</v>
       </c>
       <c r="S85" s="9">
-        <v>670</v>
+        <v>680</v>
       </c>
     </row>
     <row r="86" ht="23" customHeight="1">
@@ -5536,13 +5539,13 @@
         <v>46160</v>
       </c>
       <c r="E86" s="7">
-        <v>46113</v>
+        <v>46119</v>
       </c>
       <c r="F86" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G86" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H86" s="6" t="s">
         <v>23</v>
@@ -5551,22 +5554,22 @@
         <v>23</v>
       </c>
       <c r="J86" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="K86" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L86" s="6" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="M86" s="6" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>23</v>
@@ -5575,7 +5578,7 @@
         <v>39</v>
       </c>
       <c r="R86" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S86" s="9">
         <v>680</v>
@@ -5595,13 +5598,13 @@
         <v>46160</v>
       </c>
       <c r="E87" s="7">
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="F87" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G87" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H87" s="6" t="s">
         <v>23</v>
@@ -5610,22 +5613,22 @@
         <v>23</v>
       </c>
       <c r="J87" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="K87" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L87" s="6" t="s">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="M87" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N87" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O87" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P87" s="6" t="s">
         <v>23</v>
@@ -5634,7 +5637,7 @@
         <v>39</v>
       </c>
       <c r="R87" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S87" s="9">
         <v>680</v>
@@ -5654,13 +5657,13 @@
         <v>46160</v>
       </c>
       <c r="E88" s="7">
-        <v>46119</v>
+        <v>46092</v>
       </c>
       <c r="F88" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G88" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H88" s="6" t="s">
         <v>23</v>
@@ -5669,22 +5672,22 @@
         <v>23</v>
       </c>
       <c r="J88" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="K88" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L88" s="6" t="s">
-        <v>32</v>
+        <v>123</v>
       </c>
       <c r="M88" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>23</v>
@@ -5693,10 +5696,10 @@
         <v>39</v>
       </c>
       <c r="R88" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S88" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="89" ht="23" customHeight="1">
@@ -5713,13 +5716,13 @@
         <v>46160</v>
       </c>
       <c r="E89" s="7">
-        <v>46141</v>
+        <v>46099</v>
       </c>
       <c r="F89" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G89" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H89" s="6" t="s">
         <v>23</v>
@@ -5728,22 +5731,22 @@
         <v>23</v>
       </c>
       <c r="J89" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="K89" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L89" s="6" t="s">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="M89" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N89" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O89" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P89" s="6" t="s">
         <v>23</v>
@@ -5755,7 +5758,7 @@
         <v>33</v>
       </c>
       <c r="S89" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="90" ht="23" customHeight="1">
@@ -5772,13 +5775,13 @@
         <v>46160</v>
       </c>
       <c r="E90" s="7">
-        <v>46092</v>
+        <v>46119</v>
       </c>
       <c r="F90" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G90" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H90" s="6" t="s">
         <v>23</v>
@@ -5787,25 +5790,25 @@
         <v>23</v>
       </c>
       <c r="J90" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="K90" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L90" s="6" t="s">
-        <v>128</v>
+        <v>59</v>
       </c>
       <c r="M90" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q90" s="6" t="s">
         <v>39</v>
@@ -5831,13 +5834,13 @@
         <v>46160</v>
       </c>
       <c r="E91" s="7">
-        <v>46099</v>
+        <v>46148</v>
       </c>
       <c r="F91" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G91" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H91" s="6" t="s">
         <v>23</v>
@@ -5846,34 +5849,34 @@
         <v>23</v>
       </c>
       <c r="J91" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="K91" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L91" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M91" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N91" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="O91" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="P91" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q91" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R91" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="O91" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="P91" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q91" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R91" s="6" t="s">
-        <v>33</v>
-      </c>
       <c r="S91" s="9">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="92" ht="23" customHeight="1">
@@ -5890,13 +5893,13 @@
         <v>46160</v>
       </c>
       <c r="E92" s="7">
-        <v>46119</v>
+        <v>46148</v>
       </c>
       <c r="F92" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G92" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H92" s="6" t="s">
         <v>23</v>
@@ -5905,34 +5908,34 @@
         <v>23</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="K92" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L92" s="6" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="M92" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q92" s="6" t="s">
         <v>39</v>
       </c>
       <c r="R92" s="6" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="S92" s="9">
-        <v>700</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="93" ht="23" customHeight="1">
@@ -5952,10 +5955,10 @@
         <v>46148</v>
       </c>
       <c r="F93" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G93" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H93" s="6" t="s">
         <v>23</v>
@@ -5964,22 +5967,22 @@
         <v>23</v>
       </c>
       <c r="J93" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="K93" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L93" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="M93" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N93" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O93" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P93" s="6" t="s">
         <v>23</v>
@@ -5988,10 +5991,10 @@
         <v>39</v>
       </c>
       <c r="R93" s="6" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="S93" s="9">
-        <v>800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="94" ht="23" customHeight="1">
@@ -5999,19 +6002,19 @@
         <v>22</v>
       </c>
       <c r="B94" s="7">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="C94" s="7">
-        <v>46160</v>
+        <v>46113</v>
       </c>
       <c r="D94" s="7">
-        <v>46160</v>
+        <v>46150</v>
       </c>
       <c r="E94" s="7">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="F94" s="8">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G94" s="8">
         <v>11</v>
@@ -6023,22 +6026,22 @@
         <v>23</v>
       </c>
       <c r="J94" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="K94" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L94" s="6" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="M94" s="6" t="s">
-        <v>23</v>
+        <v>155</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>23</v>
@@ -6047,10 +6050,10 @@
         <v>39</v>
       </c>
       <c r="R94" s="6" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="S94" s="9">
-        <v>1200</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="95" ht="23" customHeight="1">
@@ -6058,22 +6061,22 @@
         <v>22</v>
       </c>
       <c r="B95" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="C95" s="7">
-        <v>46160</v>
+        <v>46082</v>
       </c>
       <c r="D95" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="E95" s="7">
-        <v>46148</v>
+        <v>46097</v>
       </c>
       <c r="F95" s="8">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G95" s="8">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H95" s="6" t="s">
         <v>23</v>
@@ -6082,34 +6085,34 @@
         <v>23</v>
       </c>
       <c r="J95" s="6" t="s">
-        <v>158</v>
+        <v>31</v>
       </c>
       <c r="K95" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L95" s="6" t="s">
-        <v>132</v>
+        <v>32</v>
       </c>
       <c r="M95" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N95" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O95" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P95" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q95" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R95" s="6" t="s">
-        <v>89</v>
+        <v>33</v>
       </c>
       <c r="S95" s="9">
-        <v>1200</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="96" ht="23" customHeight="1">
@@ -6120,19 +6123,19 @@
         <v>46167</v>
       </c>
       <c r="C96" s="7">
-        <v>46082</v>
+        <v>46167</v>
       </c>
       <c r="D96" s="7">
         <v>46167</v>
       </c>
       <c r="E96" s="7">
-        <v>46097</v>
+        <v>46119</v>
       </c>
       <c r="F96" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G96" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H96" s="6" t="s">
         <v>23</v>
@@ -6141,34 +6144,34 @@
         <v>23</v>
       </c>
       <c r="J96" s="6" t="s">
-        <v>31</v>
+        <v>156</v>
       </c>
       <c r="K96" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L96" s="6" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="M96" s="6" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q96" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R96" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S96" s="9">
-        <v>146.55</v>
+        <v>600</v>
       </c>
     </row>
     <row r="97" ht="23" customHeight="1">
@@ -6185,13 +6188,13 @@
         <v>46167</v>
       </c>
       <c r="E97" s="7">
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="F97" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G97" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H97" s="6" t="s">
         <v>23</v>
@@ -6200,22 +6203,22 @@
         <v>23</v>
       </c>
       <c r="J97" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="K97" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L97" s="6" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="M97" s="6" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="N97" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O97" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P97" s="6" t="s">
         <v>23</v>
@@ -6227,7 +6230,7 @@
         <v>30</v>
       </c>
       <c r="S97" s="9">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="98" ht="23" customHeight="1">
@@ -6247,10 +6250,10 @@
         <v>46141</v>
       </c>
       <c r="F98" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G98" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H98" s="6" t="s">
         <v>23</v>
@@ -6259,22 +6262,22 @@
         <v>23</v>
       </c>
       <c r="J98" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K98" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L98" s="6" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="M98" s="6" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>23</v>
@@ -6303,13 +6306,13 @@
         <v>46167</v>
       </c>
       <c r="E99" s="7">
-        <v>46141</v>
+        <v>46119</v>
       </c>
       <c r="F99" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G99" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H99" s="6" t="s">
         <v>23</v>
@@ -6318,22 +6321,22 @@
         <v>23</v>
       </c>
       <c r="J99" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K99" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L99" s="6" t="s">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="M99" s="6" t="s">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="N99" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O99" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P99" s="6" t="s">
         <v>23</v>
@@ -6342,7 +6345,7 @@
         <v>39</v>
       </c>
       <c r="R99" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S99" s="9">
         <v>620</v>
@@ -6365,10 +6368,10 @@
         <v>46119</v>
       </c>
       <c r="F100" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G100" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H100" s="6" t="s">
         <v>23</v>
@@ -6377,34 +6380,34 @@
         <v>23</v>
       </c>
       <c r="J100" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K100" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L100" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M100" s="6" t="s">
-        <v>105</v>
+        <v>23</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q100" s="6" t="s">
         <v>39</v>
       </c>
       <c r="R100" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S100" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="101" ht="23" customHeight="1">
@@ -6421,13 +6424,13 @@
         <v>46167</v>
       </c>
       <c r="E101" s="7">
-        <v>46119</v>
+        <v>46150</v>
       </c>
       <c r="F101" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G101" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H101" s="6" t="s">
         <v>23</v>
@@ -6436,25 +6439,25 @@
         <v>23</v>
       </c>
       <c r="J101" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="K101" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L101" s="6" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="M101" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N101" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O101" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P101" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q101" s="6" t="s">
         <v>39</v>
@@ -6483,10 +6486,10 @@
         <v>46119</v>
       </c>
       <c r="F102" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G102" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H102" s="6" t="s">
         <v>23</v>
@@ -6495,7 +6498,7 @@
         <v>23</v>
       </c>
       <c r="J102" s="6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="K102" s="6" t="s">
         <v>23</v>
@@ -6507,10 +6510,10 @@
         <v>61</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>23</v>
@@ -6542,10 +6545,10 @@
         <v>46127</v>
       </c>
       <c r="F103" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G103" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H103" s="6" t="s">
         <v>23</v>
@@ -6554,22 +6557,22 @@
         <v>23</v>
       </c>
       <c r="J103" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="K103" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L103" s="6" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="M103" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N103" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O103" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P103" s="6" t="s">
         <v>23</v>
@@ -6601,10 +6604,10 @@
         <v>46092</v>
       </c>
       <c r="F104" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G104" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H104" s="6" t="s">
         <v>23</v>
@@ -6613,22 +6616,22 @@
         <v>23</v>
       </c>
       <c r="J104" s="6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="K104" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L104" s="6" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="M104" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>23</v>
@@ -6660,10 +6663,10 @@
         <v>46119</v>
       </c>
       <c r="F105" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G105" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H105" s="6" t="s">
         <v>23</v>
@@ -6672,22 +6675,22 @@
         <v>23</v>
       </c>
       <c r="J105" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K105" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L105" s="6" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="M105" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N105" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O105" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P105" s="6" t="s">
         <v>23</v>
@@ -6719,10 +6722,10 @@
         <v>46113</v>
       </c>
       <c r="F106" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G106" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H106" s="6" t="s">
         <v>23</v>
@@ -6731,22 +6734,22 @@
         <v>23</v>
       </c>
       <c r="J106" s="6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K106" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L106" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M106" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>23</v>
@@ -6778,10 +6781,10 @@
         <v>46119</v>
       </c>
       <c r="F107" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G107" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H107" s="6" t="s">
         <v>23</v>
@@ -6790,22 +6793,22 @@
         <v>23</v>
       </c>
       <c r="J107" s="6" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="K107" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L107" s="6" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="M107" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N107" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O107" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P107" s="6" t="s">
         <v>23</v>
@@ -6837,10 +6840,10 @@
         <v>46119</v>
       </c>
       <c r="F108" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G108" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H108" s="6" t="s">
         <v>23</v>
@@ -6849,7 +6852,7 @@
         <v>23</v>
       </c>
       <c r="J108" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="K108" s="6" t="s">
         <v>23</v>
@@ -6861,10 +6864,10 @@
         <v>23</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>23</v>
@@ -6896,10 +6899,10 @@
         <v>46141</v>
       </c>
       <c r="F109" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G109" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H109" s="6" t="s">
         <v>23</v>
@@ -6908,22 +6911,22 @@
         <v>23</v>
       </c>
       <c r="J109" s="6" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="K109" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L109" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M109" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N109" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O109" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P109" s="6" t="s">
         <v>23</v>
@@ -6955,10 +6958,10 @@
         <v>46099</v>
       </c>
       <c r="F110" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G110" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H110" s="6" t="s">
         <v>23</v>
@@ -6967,22 +6970,22 @@
         <v>23</v>
       </c>
       <c r="J110" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K110" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L110" s="6" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="M110" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>23</v>
@@ -7014,10 +7017,10 @@
         <v>46148</v>
       </c>
       <c r="F111" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G111" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H111" s="6" t="s">
         <v>23</v>
@@ -7026,31 +7029,31 @@
         <v>23</v>
       </c>
       <c r="J111" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K111" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L111" s="6" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="M111" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N111" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="O111" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="P111" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q111" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R111" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="O111" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="P111" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q111" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R111" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="S111" s="9">
         <v>800</v>
@@ -7073,10 +7076,10 @@
         <v>46148</v>
       </c>
       <c r="F112" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G112" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H112" s="6" t="s">
         <v>23</v>
@@ -7085,22 +7088,22 @@
         <v>23</v>
       </c>
       <c r="J112" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="K112" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L112" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="M112" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>23</v>
@@ -7109,7 +7112,7 @@
         <v>39</v>
       </c>
       <c r="R112" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="S112" s="9">
         <v>1200</v>
@@ -7132,10 +7135,10 @@
         <v>46148</v>
       </c>
       <c r="F113" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G113" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H113" s="6" t="s">
         <v>23</v>
@@ -7144,22 +7147,22 @@
         <v>23</v>
       </c>
       <c r="J113" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="K113" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L113" s="6" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="M113" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N113" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O113" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P113" s="6" t="s">
         <v>23</v>
@@ -7168,7 +7171,7 @@
         <v>39</v>
       </c>
       <c r="R113" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="S113" s="9">
         <v>1200</v>
@@ -7179,117 +7182,176 @@
         <v>22</v>
       </c>
       <c r="B114" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C114" s="7">
+        <v>46113</v>
+      </c>
+      <c r="D114" s="7">
+        <v>46150</v>
+      </c>
+      <c r="E114" s="7">
+        <v>46149</v>
+      </c>
+      <c r="F114" s="8">
+        <v>0</v>
+      </c>
+      <c r="G114" s="8">
+        <v>17</v>
+      </c>
+      <c r="H114" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I114" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J114" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="K114" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L114" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="M114" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="N114" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="O114" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="P114" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q114" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R114" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S114" s="9">
+        <v>4400</v>
+      </c>
+    </row>
+    <row r="115" ht="23" customHeight="1">
+      <c r="A115" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B115" s="7">
         <v>46172</v>
       </c>
-      <c r="C114" s="7">
+      <c r="C115" s="7">
         <v>45930</v>
       </c>
-      <c r="D114" s="7">
+      <c r="D115" s="7">
         <v>46172</v>
       </c>
-      <c r="E114" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F114" s="8">
-        <v>23</v>
-      </c>
-      <c r="G114" s="8">
-        <v>23</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I114" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J114" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="K114" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L114" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="M114" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N114" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="O114" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="P114" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q114" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R114" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="S114" s="9">
+      <c r="E115" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F115" s="8">
+        <v>22</v>
+      </c>
+      <c r="G115" s="8">
+        <v>22</v>
+      </c>
+      <c r="H115" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I115" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J115" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K115" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L115" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M115" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N115" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="O115" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="P115" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q115" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R115" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="S115" s="9">
         <v>185.5</v>
       </c>
     </row>
-    <row r="115" ht="23" customHeight="1">
-      <c r="A115" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B115" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C115" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D115" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E115" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F115" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G115" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H115" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I115" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J115" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="K115" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="L115" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M115" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="N115" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="O115" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="P115" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q115" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="R115" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="S115" s="13">
-        <f>SUM(S6:S114)</f>
+    <row r="116" ht="23" customHeight="1">
+      <c r="A116" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B116" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C116" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D116" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E116" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F116" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G116" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H116" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I116" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J116" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K116" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L116" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M116" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="N116" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="O116" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="P116" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q116" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="R116" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S116" s="13">
+        <f>SUM(S6:S115)</f>
       </c>
     </row>
   </sheetData>

--- a/docx_templates/CONTAS-A-RECEBER.xlsx
+++ b/docx_templates/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$112</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$76</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="140">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -36,11 +36,11 @@
         <color rgb="FF808080"/>
         <sz val="11"/>
       </rPr>
-      <t>Data Inicial: 01/08/2025, Data Final: 31/05/2026, Conta de Recebimento: 1.0 [OFICIAL] SICREDI | BANCO GESTOR</t>
+      <t>Data Inicial: 01/08/2025, Data Final: 18/05/2026, Conta de Recebimento: 1.0 [OFICIAL] SICREDI | BANCO GESTOR</t>
     </r>
   </si>
   <si>
-    <t>Relatório exportado em terça-feira, 12 de maio de 2026 por KAROL MEDEIROS</t>
+    <t>Relatório exportado em quarta-feira, 13 de maio de 2026 por KAROL MEDEIROS</t>
   </si>
   <si>
     <t>Conta de Recebimento</t>
@@ -160,418 +160,298 @@
     <t>FA-11390</t>
   </si>
   <si>
-    <t>FA-11552</t>
+    <t>FA-11446</t>
+  </si>
+  <si>
+    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
+  </si>
+  <si>
+    <t>ND-11574</t>
+  </si>
+  <si>
+    <t>REGINALDO BENTO DA SILVA</t>
+  </si>
+  <si>
+    <t>JOÃO PAULO CONSÓRCIOS</t>
+  </si>
+  <si>
+    <t>FA-11452</t>
+  </si>
+  <si>
+    <t>YAGO ELIAS COSTA BATISTA</t>
+  </si>
+  <si>
+    <t>FA-11410</t>
+  </si>
+  <si>
+    <t>DAVI HENRIQUE DANTAS DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-11255</t>
+  </si>
+  <si>
+    <t>FA-11461</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11460</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
+    <t>FA-11356</t>
+  </si>
+  <si>
+    <t>ANDERSON QUEIROZ PINHEIRO</t>
+  </si>
+  <si>
+    <t>FA-11458</t>
+  </si>
+  <si>
+    <t>FA-11464</t>
+  </si>
+  <si>
+    <t>FA-11553</t>
+  </si>
+  <si>
+    <t>YURI BATISTA DA COSTA</t>
+  </si>
+  <si>
+    <t>FA-11396</t>
+  </si>
+  <si>
+    <t>FA-11466</t>
+  </si>
+  <si>
+    <t>FA-11424</t>
+  </si>
+  <si>
+    <t>OLIZIEL DA SILVA CARDOSO</t>
+  </si>
+  <si>
+    <t>FA-11468</t>
+  </si>
+  <si>
+    <t>FA-11351</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-11614</t>
+  </si>
+  <si>
+    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11587</t>
+  </si>
+  <si>
+    <t>JACKSON CASSIANO VERISSIMO</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
+  </si>
+  <si>
+    <t>FA-11114</t>
+  </si>
+  <si>
+    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
+  </si>
+  <si>
+    <t>FA-11355</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
+    <t>FA-11496</t>
+  </si>
+  <si>
+    <t>ANDRE CAVALCANTI DA FE</t>
+  </si>
+  <si>
+    <t>FA-11618</t>
+  </si>
+  <si>
+    <t>DANILO DE ALMEIDA TORRES</t>
+  </si>
+  <si>
+    <t>VENCIDO ACIMA DE 90 DIAS</t>
+  </si>
+  <si>
+    <t>ND-10427</t>
+  </si>
+  <si>
+    <t>FA-11497</t>
+  </si>
+  <si>
+    <t>FA-11471</t>
+  </si>
+  <si>
+    <t>FA-11522</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>FA-11476</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>FA-11557</t>
+  </si>
+  <si>
+    <t>FA-11556</t>
   </si>
   <si>
     <t>DIEGO TAYAO DANTAS</t>
   </si>
   <si>
-    <t>FA-11497</t>
-  </si>
-  <si>
-    <t>ANDRE CAVALCANTI DA FE</t>
-  </si>
-  <si>
-    <t>FA-11446</t>
-  </si>
-  <si>
-    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
-  </si>
-  <si>
-    <t>ND-11574</t>
-  </si>
-  <si>
-    <t>REGINALDO BENTO DA SILVA</t>
-  </si>
-  <si>
-    <t>JOÃO PAULO CONSÓRCIOS</t>
-  </si>
-  <si>
-    <t>FA-11452</t>
-  </si>
-  <si>
-    <t>YAGO ELIAS COSTA BATISTA</t>
-  </si>
-  <si>
-    <t>FA-11410</t>
-  </si>
-  <si>
-    <t>DAVI HENRIQUE DANTAS DE SOUZA</t>
-  </si>
-  <si>
-    <t>FA-11255</t>
-  </si>
-  <si>
-    <t>FA-11461</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11460</t>
-  </si>
-  <si>
-    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
-  </si>
-  <si>
-    <t>FA-11356</t>
-  </si>
-  <si>
-    <t>ANDERSON QUEIROZ PINHEIRO</t>
-  </si>
-  <si>
-    <t>FA-11458</t>
-  </si>
-  <si>
-    <t>VENCIDO ACIMA DE 90 DIAS</t>
-  </si>
-  <si>
-    <t>ND-10427</t>
-  </si>
-  <si>
-    <t>RICARDO ARAUJO DE MIRANDA</t>
-  </si>
-  <si>
-    <t>FA-11464</t>
-  </si>
-  <si>
-    <t>FA-11555</t>
-  </si>
-  <si>
-    <t>FA-11553</t>
-  </si>
-  <si>
-    <t>YURI BATISTA DA COSTA</t>
-  </si>
-  <si>
-    <t>FA-11396</t>
-  </si>
-  <si>
-    <t>FA-11466</t>
-  </si>
-  <si>
-    <t>FA-11424</t>
-  </si>
-  <si>
-    <t>OLIZIEL DA SILVA CARDOSO</t>
-  </si>
-  <si>
-    <t>FA-11468</t>
-  </si>
-  <si>
-    <t>FA-11351</t>
-  </si>
-  <si>
-    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
-  </si>
-  <si>
-    <t>FA-11354</t>
-  </si>
-  <si>
-    <t>FA-11614</t>
-  </si>
-  <si>
-    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11587</t>
-  </si>
-  <si>
-    <t>JACKSON CASSIANO VERISSIMO</t>
-  </si>
-  <si>
-    <t>LUZ DIVINA LTDA</t>
-  </si>
-  <si>
-    <t>FA-11114</t>
-  </si>
-  <si>
-    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
-  </si>
-  <si>
-    <t>FA-11355</t>
-  </si>
-  <si>
-    <t>FA-11496</t>
-  </si>
-  <si>
-    <t>FA-11618</t>
-  </si>
-  <si>
-    <t>DANILO DE ALMEIDA TORRES</t>
-  </si>
-  <si>
-    <t>FA-11397</t>
+    <t>FA-11615</t>
+  </si>
+  <si>
+    <t>FA-11523</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11398</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>FA-11399</t>
+  </si>
+  <si>
+    <t>FA-11278</t>
+  </si>
+  <si>
+    <t>FELIPE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11473</t>
+  </si>
+  <si>
+    <t>FA-11475</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>FA-11478</t>
+  </si>
+  <si>
+    <t>FA-11558</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11267</t>
+  </si>
+  <si>
+    <t>ANNY KATARINA ACIOLE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11472</t>
+  </si>
+  <si>
+    <t>FA-11453</t>
+  </si>
+  <si>
+    <t>A VENCER</t>
+  </si>
+  <si>
+    <t>FA-11474</t>
+  </si>
+  <si>
+    <t>FA-11400</t>
   </si>
   <si>
     <t>JOZILDO TARQUINO DE BRITO</t>
   </si>
   <si>
-    <t>FA-11471</t>
-  </si>
-  <si>
-    <t>FA-11522</t>
-  </si>
-  <si>
-    <t>ROBERTO MURATORI</t>
-  </si>
-  <si>
-    <t>FA-11557</t>
-  </si>
-  <si>
-    <t>FA-11556</t>
-  </si>
-  <si>
-    <t>FA-11476</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>FA-11398</t>
-  </si>
-  <si>
-    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
-  </si>
-  <si>
-    <t>FA-11399</t>
-  </si>
-  <si>
-    <t>FA-11492</t>
+    <t>FA-11525</t>
+  </si>
+  <si>
+    <t>FA-11481</t>
+  </si>
+  <si>
+    <t>FA-11559</t>
+  </si>
+  <si>
+    <t>FA-11560</t>
+  </si>
+  <si>
+    <t>FA-11616</t>
+  </si>
+  <si>
+    <t>FA-11526</t>
+  </si>
+  <si>
+    <t>FA-11493</t>
   </si>
   <si>
     <t>ROSSILY PEREIRA DA SILVA</t>
   </si>
   <si>
-    <t>FA-11523</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11615</t>
-  </si>
-  <si>
-    <t>FA-11502</t>
+    <t>FA-11401</t>
+  </si>
+  <si>
+    <t>FA-11402</t>
+  </si>
+  <si>
+    <t>FA-11279</t>
+  </si>
+  <si>
+    <t>FA-11503</t>
   </si>
   <si>
     <t>WESCLY JEAN DE MEDEIROS</t>
   </si>
   <si>
-    <t>FA-11473</t>
-  </si>
-  <si>
-    <t>FA-11278</t>
-  </si>
-  <si>
-    <t>FELIPE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11432</t>
+    <t>FA-11482</t>
+  </si>
+  <si>
+    <t>FA-11620</t>
+  </si>
+  <si>
+    <t>FA-11433</t>
   </si>
   <si>
     <t>RAYANE ROBERTA DA SILVA</t>
   </si>
   <si>
-    <t>FA-11475</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
-    <t>FA-11478</t>
-  </si>
-  <si>
-    <t>FA-11558</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11472</t>
-  </si>
-  <si>
-    <t>FA-11327</t>
+    <t>FA-11561</t>
+  </si>
+  <si>
+    <t>FA-11483</t>
+  </si>
+  <si>
+    <t>FA-11484</t>
+  </si>
+  <si>
+    <t>FA-11411</t>
+  </si>
+  <si>
+    <t>FA-11268</t>
+  </si>
+  <si>
+    <t>FA-11328</t>
   </si>
   <si>
     <t>MAICON LOPES SILVA</t>
   </si>
   <si>
-    <t>FA-11267</t>
-  </si>
-  <si>
-    <t>ANNY KATARINA ACIOLE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11599</t>
-  </si>
-  <si>
-    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>FA-11575</t>
-  </si>
-  <si>
-    <t>ADRIANO TEOTONIO DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11453</t>
-  </si>
-  <si>
-    <t>HOJE</t>
-  </si>
-  <si>
-    <t>A VENCER</t>
-  </si>
-  <si>
-    <t>FA-11400</t>
-  </si>
-  <si>
-    <t>FA-11474</t>
-  </si>
-  <si>
-    <t>FA-11525</t>
-  </si>
-  <si>
-    <t>FA-11481</t>
-  </si>
-  <si>
-    <t>FA-11559</t>
-  </si>
-  <si>
-    <t>FA-11560</t>
-  </si>
-  <si>
-    <t>FA-11493</t>
-  </si>
-  <si>
-    <t>FA-11526</t>
-  </si>
-  <si>
-    <t>FA-11401</t>
-  </si>
-  <si>
-    <t>FA-11402</t>
-  </si>
-  <si>
-    <t>FA-11616</t>
-  </si>
-  <si>
-    <t>FA-11620</t>
-  </si>
-  <si>
-    <t>FA-11279</t>
-  </si>
-  <si>
-    <t>FA-11503</t>
-  </si>
-  <si>
-    <t>FA-11482</t>
-  </si>
-  <si>
-    <t>FA-11433</t>
-  </si>
-  <si>
-    <t>FA-11411</t>
-  </si>
-  <si>
-    <t>FA-11483</t>
-  </si>
-  <si>
-    <t>FA-11484</t>
-  </si>
-  <si>
-    <t>FA-11561</t>
-  </si>
-  <si>
-    <t>FA-11268</t>
-  </si>
-  <si>
-    <t>FA-11328</t>
-  </si>
-  <si>
     <t>FA-11479</t>
-  </si>
-  <si>
-    <t>FA-11600</t>
-  </si>
-  <si>
-    <t>FA-11590</t>
-  </si>
-  <si>
-    <t>FA-11577</t>
-  </si>
-  <si>
-    <t>FA-11611</t>
-  </si>
-  <si>
-    <t>M&amp;S DO TRABALHO</t>
-  </si>
-  <si>
-    <t>FA-11480</t>
-  </si>
-  <si>
-    <t>FA-11562</t>
-  </si>
-  <si>
-    <t>FA-11563</t>
-  </si>
-  <si>
-    <t>FA-11487</t>
-  </si>
-  <si>
-    <t>FA-11494</t>
-  </si>
-  <si>
-    <t>FA-11617</t>
-  </si>
-  <si>
-    <t>FA-11621</t>
-  </si>
-  <si>
-    <t>FA-11488</t>
-  </si>
-  <si>
-    <t>FA-11504</t>
-  </si>
-  <si>
-    <t>FA-11280</t>
-  </si>
-  <si>
-    <t>FA-11434</t>
-  </si>
-  <si>
-    <t>FA-11412</t>
-  </si>
-  <si>
-    <t>FA-11489</t>
-  </si>
-  <si>
-    <t>FA-11491</t>
-  </si>
-  <si>
-    <t>FA-11564</t>
-  </si>
-  <si>
-    <t>FA-11329</t>
-  </si>
-  <si>
-    <t>FA-11601</t>
-  </si>
-  <si>
-    <t>FA-11591</t>
-  </si>
-  <si>
-    <t>FA-11578</t>
-  </si>
-  <si>
-    <t>FA-11613</t>
-  </si>
-  <si>
-    <t>SEGCOMP</t>
-  </si>
-  <si>
-    <t>SEGCOMP TECNOLOGIA LTDA</t>
   </si>
 </sst>
 </file>
@@ -714,7 +594,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S118"/>
+  <dimension ref="A1:S82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.13657760620117" customWidth="1" style="1"/>
@@ -831,10 +711,10 @@
         <v>23</v>
       </c>
       <c r="F6" s="8">
-        <v>-36</v>
+        <v>-37</v>
       </c>
       <c r="G6" s="8">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>24</v>
@@ -890,10 +770,10 @@
         <v>23</v>
       </c>
       <c r="F7" s="8">
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="G7" s="8">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>25</v>
@@ -949,10 +829,10 @@
         <v>23</v>
       </c>
       <c r="F8" s="8">
-        <v>-43</v>
+        <v>-44</v>
       </c>
       <c r="G8" s="8">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>24</v>
@@ -1008,10 +888,10 @@
         <v>23</v>
       </c>
       <c r="F9" s="8">
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="G9" s="8">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>25</v>
@@ -1067,10 +947,10 @@
         <v>46127</v>
       </c>
       <c r="F10" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="G10" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>25</v>
@@ -1126,10 +1006,10 @@
         <v>46097</v>
       </c>
       <c r="F11" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="G11" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>25</v>
@@ -1185,10 +1065,10 @@
         <v>23</v>
       </c>
       <c r="F12" s="8">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="G12" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>25</v>
@@ -1232,19 +1112,19 @@
         <v>22</v>
       </c>
       <c r="B13" s="7">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C13" s="7">
-        <v>46139</v>
+        <v>46082</v>
       </c>
       <c r="D13" s="7">
-        <v>46139</v>
-      </c>
-      <c r="E13" s="7">
-        <v>46141</v>
+        <v>46132</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F13" s="8">
-        <v>-15</v>
+        <v>-23</v>
       </c>
       <c r="G13" s="8">
         <v>-15</v>
@@ -1256,16 +1136,16 @@
         <v>25</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="N13" s="6" t="s">
         <v>28</v>
@@ -1277,13 +1157,13 @@
         <v>23</v>
       </c>
       <c r="Q13" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S13" s="9">
-        <v>620</v>
+        <v>104.04</v>
       </c>
     </row>
     <row r="14" ht="23" customHeight="1">
@@ -1291,19 +1171,19 @@
         <v>22</v>
       </c>
       <c r="B14" s="7">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C14" s="7">
-        <v>46139</v>
+        <v>46125</v>
       </c>
       <c r="D14" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E14" s="7">
-        <v>46122</v>
+        <v>46125</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F14" s="8">
-        <v>-22</v>
+        <v>-30</v>
       </c>
       <c r="G14" s="8">
         <v>-15</v>
@@ -1315,13 +1195,13 @@
         <v>25</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K14" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="M14" s="6" t="s">
         <v>23</v>
@@ -1336,13 +1216,13 @@
         <v>23</v>
       </c>
       <c r="Q14" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R14" s="6" t="s">
         <v>33</v>
       </c>
       <c r="S14" s="9">
-        <v>650</v>
+        <v>408.24</v>
       </c>
     </row>
     <row r="15" ht="23" customHeight="1">
@@ -1350,22 +1230,22 @@
         <v>22</v>
       </c>
       <c r="B15" s="7">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="C15" s="7">
-        <v>46082</v>
+        <v>45930</v>
       </c>
       <c r="D15" s="7">
-        <v>46132</v>
+        <v>46142</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F15" s="8">
-        <v>-22</v>
+        <v>-13</v>
       </c>
       <c r="G15" s="8">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>25</v>
@@ -1374,13 +1254,13 @@
         <v>25</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="M15" s="6" t="s">
         <v>23</v>
@@ -1398,10 +1278,10 @@
         <v>23</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="S15" s="9">
-        <v>104.04</v>
+        <v>185.5</v>
       </c>
     </row>
     <row r="16" ht="23" customHeight="1">
@@ -1409,22 +1289,22 @@
         <v>22</v>
       </c>
       <c r="B16" s="7">
-        <v>46140</v>
+        <v>46146</v>
       </c>
       <c r="C16" s="7">
-        <v>46125</v>
+        <v>46113</v>
       </c>
       <c r="D16" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>23</v>
+        <v>46150</v>
+      </c>
+      <c r="E16" s="7">
+        <v>46141</v>
       </c>
       <c r="F16" s="8">
-        <v>-29</v>
+        <v>-5</v>
       </c>
       <c r="G16" s="8">
-        <v>-14</v>
+        <v>-9</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>25</v>
@@ -1433,34 +1313,34 @@
         <v>25</v>
       </c>
       <c r="J16" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N16" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="O16" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="P16" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q16" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="R16" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="K16" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L16" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="M16" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N16" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="O16" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="P16" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q16" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R16" s="6" t="s">
-        <v>33</v>
-      </c>
       <c r="S16" s="9">
-        <v>408.24</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="17" ht="23" customHeight="1">
@@ -1468,22 +1348,22 @@
         <v>22</v>
       </c>
       <c r="B17" s="7">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="C17" s="7">
-        <v>45930</v>
+        <v>46132</v>
       </c>
       <c r="D17" s="7">
-        <v>46142</v>
+        <v>46132</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F17" s="8">
-        <v>-12</v>
+        <v>-23</v>
       </c>
       <c r="G17" s="8">
-        <v>-12</v>
+        <v>-9</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>25</v>
@@ -1492,16 +1372,16 @@
         <v>25</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="K17" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="N17" s="6" t="s">
         <v>28</v>
@@ -1516,10 +1396,10 @@
         <v>23</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="S17" s="9">
-        <v>185.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" ht="23" customHeight="1">
@@ -1530,19 +1410,19 @@
         <v>46146</v>
       </c>
       <c r="C18" s="7">
-        <v>46113</v>
+        <v>46153</v>
       </c>
       <c r="D18" s="7">
-        <v>46150</v>
-      </c>
-      <c r="E18" s="7">
-        <v>46141</v>
+        <v>46153</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F18" s="8">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="G18" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>25</v>
@@ -1551,16 +1431,16 @@
         <v>25</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="N18" s="6" t="s">
         <v>28</v>
@@ -1572,13 +1452,13 @@
         <v>23</v>
       </c>
       <c r="Q18" s="6" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="S18" s="9">
-        <v>12.9</v>
+        <v>61.21</v>
       </c>
     </row>
     <row r="19" ht="23" customHeight="1">
@@ -1589,19 +1469,19 @@
         <v>46146</v>
       </c>
       <c r="C19" s="7">
-        <v>46132</v>
+        <v>46125</v>
       </c>
       <c r="D19" s="7">
-        <v>46132</v>
+        <v>46125</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F19" s="8">
-        <v>-22</v>
+        <v>-30</v>
       </c>
       <c r="G19" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>25</v>
@@ -1616,10 +1496,10 @@
         <v>23</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="N19" s="6" t="s">
         <v>28</v>
@@ -1637,7 +1517,7 @@
         <v>30</v>
       </c>
       <c r="S19" s="9">
-        <v>50</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" ht="23" customHeight="1">
@@ -1648,19 +1528,19 @@
         <v>46146</v>
       </c>
       <c r="C20" s="7">
-        <v>46153</v>
+        <v>46082</v>
       </c>
       <c r="D20" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>23</v>
+        <v>46146</v>
+      </c>
+      <c r="E20" s="7">
+        <v>46097</v>
       </c>
       <c r="F20" s="8">
-        <v>-1</v>
+        <v>-9</v>
       </c>
       <c r="G20" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>25</v>
@@ -1669,16 +1549,16 @@
         <v>25</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="N20" s="6" t="s">
         <v>28</v>
@@ -1690,13 +1570,13 @@
         <v>23</v>
       </c>
       <c r="Q20" s="6" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S20" s="9">
-        <v>61.21</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="21" ht="23" customHeight="1">
@@ -1707,19 +1587,19 @@
         <v>46146</v>
       </c>
       <c r="C21" s="7">
-        <v>46125</v>
+        <v>46139</v>
       </c>
       <c r="D21" s="7">
-        <v>46125</v>
+        <v>46139</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F21" s="8">
-        <v>-29</v>
+        <v>-16</v>
       </c>
       <c r="G21" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>25</v>
@@ -1728,13 +1608,13 @@
         <v>25</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>23</v>
@@ -1746,7 +1626,7 @@
         <v>28</v>
       </c>
       <c r="P21" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q21" s="6" t="s">
         <v>23</v>
@@ -1755,7 +1635,7 @@
         <v>30</v>
       </c>
       <c r="S21" s="9">
-        <v>80</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" ht="23" customHeight="1">
@@ -1766,19 +1646,19 @@
         <v>46146</v>
       </c>
       <c r="C22" s="7">
-        <v>46082</v>
+        <v>46139</v>
       </c>
       <c r="D22" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E22" s="7">
-        <v>46097</v>
+        <v>46139</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F22" s="8">
-        <v>-8</v>
+        <v>-16</v>
       </c>
       <c r="G22" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>25</v>
@@ -1787,16 +1667,16 @@
         <v>25</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="N22" s="6" t="s">
         <v>28</v>
@@ -1808,13 +1688,13 @@
         <v>23</v>
       </c>
       <c r="Q22" s="6" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S22" s="9">
-        <v>146.55</v>
+        <v>204.67</v>
       </c>
     </row>
     <row r="23" ht="23" customHeight="1">
@@ -1825,19 +1705,19 @@
         <v>46146</v>
       </c>
       <c r="C23" s="7">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="D23" s="7">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F23" s="8">
-        <v>-15</v>
+        <v>-9</v>
       </c>
       <c r="G23" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>25</v>
@@ -1864,7 +1744,7 @@
         <v>28</v>
       </c>
       <c r="P23" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q23" s="6" t="s">
         <v>23</v>
@@ -1873,7 +1753,7 @@
         <v>30</v>
       </c>
       <c r="S23" s="9">
-        <v>150</v>
+        <v>205.82</v>
       </c>
     </row>
     <row r="24" ht="23" customHeight="1">
@@ -1893,10 +1773,10 @@
         <v>23</v>
       </c>
       <c r="F24" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="G24" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>25</v>
@@ -1911,10 +1791,10 @@
         <v>23</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="N24" s="6" t="s">
         <v>28</v>
@@ -1932,7 +1812,7 @@
         <v>30</v>
       </c>
       <c r="S24" s="9">
-        <v>204.67</v>
+        <v>350</v>
       </c>
     </row>
     <row r="25" ht="23" customHeight="1">
@@ -1948,14 +1828,14 @@
       <c r="D25" s="7">
         <v>46146</v>
       </c>
-      <c r="E25" s="7" t="s">
-        <v>23</v>
+      <c r="E25" s="7">
+        <v>46119</v>
       </c>
       <c r="F25" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G25" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>25</v>
@@ -1964,16 +1844,16 @@
         <v>25</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K25" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="N25" s="6" t="s">
         <v>28</v>
@@ -1985,13 +1865,13 @@
         <v>23</v>
       </c>
       <c r="Q25" s="6" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="R25" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S25" s="9">
-        <v>205.82</v>
+        <v>600</v>
       </c>
     </row>
     <row r="26" ht="23" customHeight="1">
@@ -2002,19 +1882,19 @@
         <v>46146</v>
       </c>
       <c r="C26" s="7">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="D26" s="7">
-        <v>46139</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>23</v>
+        <v>46146</v>
+      </c>
+      <c r="E26" s="7">
+        <v>46141</v>
       </c>
       <c r="F26" s="8">
-        <v>-15</v>
+        <v>-9</v>
       </c>
       <c r="G26" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>25</v>
@@ -2023,16 +1903,16 @@
         <v>25</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K26" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="N26" s="6" t="s">
         <v>28</v>
@@ -2044,13 +1924,13 @@
         <v>23</v>
       </c>
       <c r="Q26" s="6" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="R26" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S26" s="9">
-        <v>350</v>
+        <v>620</v>
       </c>
     </row>
     <row r="27" ht="23" customHeight="1">
@@ -2061,34 +1941,34 @@
         <v>46146</v>
       </c>
       <c r="C27" s="7">
-        <v>45901</v>
+        <v>46146</v>
       </c>
       <c r="D27" s="7">
-        <v>45938</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>23</v>
+        <v>46146</v>
+      </c>
+      <c r="E27" s="7">
+        <v>46112</v>
       </c>
       <c r="F27" s="8">
-        <v>-216</v>
+        <v>-9</v>
       </c>
       <c r="G27" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="I27" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K27" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="M27" s="6" t="s">
         <v>23</v>
@@ -2103,13 +1983,13 @@
         <v>23</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="R27" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S27" s="9">
-        <v>363</v>
+        <v>630</v>
       </c>
     </row>
     <row r="28" ht="23" customHeight="1">
@@ -2129,10 +2009,10 @@
         <v>46119</v>
       </c>
       <c r="F28" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G28" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>25</v>
@@ -2141,16 +2021,16 @@
         <v>25</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N28" s="6" t="s">
         <v>28</v>
@@ -2168,7 +2048,7 @@
         <v>30</v>
       </c>
       <c r="S28" s="9">
-        <v>600</v>
+        <v>650</v>
       </c>
     </row>
     <row r="29" ht="23" customHeight="1">
@@ -2179,19 +2059,19 @@
         <v>46146</v>
       </c>
       <c r="C29" s="7">
-        <v>46146</v>
+        <v>46132</v>
       </c>
       <c r="D29" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E29" s="7">
-        <v>46141</v>
+        <v>46132</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F29" s="8">
-        <v>-8</v>
+        <v>-23</v>
       </c>
       <c r="G29" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>25</v>
@@ -2200,16 +2080,16 @@
         <v>25</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="N29" s="6" t="s">
         <v>28</v>
@@ -2221,13 +2101,13 @@
         <v>23</v>
       </c>
       <c r="Q29" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R29" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S29" s="9">
-        <v>620</v>
+        <v>655.21</v>
       </c>
     </row>
     <row r="30" ht="23" customHeight="1">
@@ -2244,13 +2124,13 @@
         <v>46146</v>
       </c>
       <c r="E30" s="7">
-        <v>46141</v>
+        <v>46119</v>
       </c>
       <c r="F30" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G30" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>25</v>
@@ -2259,13 +2139,13 @@
         <v>25</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="M30" s="6" t="s">
         <v>23</v>
@@ -2277,7 +2157,7 @@
         <v>28</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q30" s="6" t="s">
         <v>39</v>
@@ -2286,7 +2166,7 @@
         <v>30</v>
       </c>
       <c r="S30" s="9">
-        <v>620</v>
+        <v>700</v>
       </c>
     </row>
     <row r="31" ht="23" customHeight="1">
@@ -2294,19 +2174,19 @@
         <v>22</v>
       </c>
       <c r="B31" s="7">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="C31" s="7">
-        <v>46146</v>
+        <v>46139</v>
       </c>
       <c r="D31" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E31" s="7">
-        <v>46112</v>
+        <v>46139</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F31" s="8">
-        <v>-8</v>
+        <v>-16</v>
       </c>
       <c r="G31" s="8">
         <v>-8</v>
@@ -2318,13 +2198,13 @@
         <v>25</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="M31" s="6" t="s">
         <v>23</v>
@@ -2339,13 +2219,13 @@
         <v>23</v>
       </c>
       <c r="Q31" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R31" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S31" s="9">
-        <v>630</v>
+        <v>103.36</v>
       </c>
     </row>
     <row r="32" ht="23" customHeight="1">
@@ -2353,7 +2233,7 @@
         <v>22</v>
       </c>
       <c r="B32" s="7">
-        <v>46146</v>
+        <v>46149</v>
       </c>
       <c r="C32" s="7">
         <v>46146</v>
@@ -2361,14 +2241,14 @@
       <c r="D32" s="7">
         <v>46146</v>
       </c>
-      <c r="E32" s="7">
-        <v>46119</v>
+      <c r="E32" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F32" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G32" s="8">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>25</v>
@@ -2377,16 +2257,16 @@
         <v>25</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="N32" s="6" t="s">
         <v>28</v>
@@ -2398,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R32" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S32" s="9">
-        <v>650</v>
+        <v>380</v>
       </c>
     </row>
     <row r="33" ht="23" customHeight="1">
@@ -2412,22 +2292,22 @@
         <v>22</v>
       </c>
       <c r="B33" s="7">
-        <v>46146</v>
+        <v>46149</v>
       </c>
       <c r="C33" s="7">
-        <v>46132</v>
+        <v>46142</v>
       </c>
       <c r="D33" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>23</v>
+        <v>46142</v>
+      </c>
+      <c r="E33" s="7">
+        <v>46148</v>
       </c>
       <c r="F33" s="8">
-        <v>-22</v>
+        <v>-13</v>
       </c>
       <c r="G33" s="8">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>25</v>
@@ -2436,34 +2316,34 @@
         <v>25</v>
       </c>
       <c r="J33" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="K33" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L33" s="6" t="s">
+      <c r="M33" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N33" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="O33" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="P33" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q33" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R33" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="M33" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N33" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="O33" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="P33" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q33" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R33" s="6" t="s">
-        <v>30</v>
-      </c>
       <c r="S33" s="9">
-        <v>655.21</v>
+        <v>685.71</v>
       </c>
     </row>
     <row r="34" ht="23" customHeight="1">
@@ -2471,22 +2351,22 @@
         <v>22</v>
       </c>
       <c r="B34" s="7">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="C34" s="7">
-        <v>46146</v>
+        <v>46125</v>
       </c>
       <c r="D34" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E34" s="7">
-        <v>46119</v>
+        <v>46125</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F34" s="8">
-        <v>-8</v>
+        <v>-30</v>
       </c>
       <c r="G34" s="8">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>25</v>
@@ -2501,7 +2381,7 @@
         <v>23</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="M34" s="6" t="s">
         <v>23</v>
@@ -2513,16 +2393,16 @@
         <v>28</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R34" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S34" s="9">
-        <v>700</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="35" ht="23" customHeight="1">
@@ -2530,22 +2410,22 @@
         <v>22</v>
       </c>
       <c r="B35" s="7">
-        <v>46147</v>
+        <v>46150</v>
       </c>
       <c r="C35" s="7">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="D35" s="7">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F35" s="8">
-        <v>-15</v>
+        <v>-9</v>
       </c>
       <c r="G35" s="8">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>25</v>
@@ -2554,13 +2434,13 @@
         <v>25</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>23</v>
@@ -2581,7 +2461,7 @@
         <v>30</v>
       </c>
       <c r="S35" s="9">
-        <v>103.36</v>
+        <v>170</v>
       </c>
     </row>
     <row r="36" ht="23" customHeight="1">
@@ -2589,22 +2469,22 @@
         <v>22</v>
       </c>
       <c r="B36" s="7">
-        <v>46147</v>
+        <v>46150</v>
       </c>
       <c r="C36" s="7">
-        <v>46146</v>
+        <v>46125</v>
       </c>
       <c r="D36" s="7">
-        <v>46146</v>
+        <v>46125</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F36" s="8">
-        <v>-8</v>
+        <v>-30</v>
       </c>
       <c r="G36" s="8">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>25</v>
@@ -2613,13 +2493,13 @@
         <v>25</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>23</v>
@@ -2637,10 +2517,10 @@
         <v>23</v>
       </c>
       <c r="R36" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S36" s="9">
-        <v>124.27</v>
+        <v>250</v>
       </c>
     </row>
     <row r="37" ht="23" customHeight="1">
@@ -2648,19 +2528,19 @@
         <v>22</v>
       </c>
       <c r="B37" s="7">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="C37" s="7">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="D37" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>23</v>
+        <v>46150</v>
+      </c>
+      <c r="E37" s="7">
+        <v>46153</v>
       </c>
       <c r="F37" s="8">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="G37" s="8">
         <v>-5</v>
@@ -2672,13 +2552,13 @@
         <v>25</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>23</v>
@@ -2693,13 +2573,13 @@
         <v>23</v>
       </c>
       <c r="Q37" s="6" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="R37" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S37" s="9">
-        <v>380</v>
+        <v>278.57</v>
       </c>
     </row>
     <row r="38" ht="23" customHeight="1">
@@ -2707,37 +2587,37 @@
         <v>22</v>
       </c>
       <c r="B38" s="7">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="C38" s="7">
-        <v>46142</v>
+        <v>45901</v>
       </c>
       <c r="D38" s="7">
-        <v>46142</v>
-      </c>
-      <c r="E38" s="7">
-        <v>46148</v>
+        <v>45938</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F38" s="8">
-        <v>-12</v>
+        <v>-217</v>
       </c>
       <c r="G38" s="8">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="I38" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>23</v>
@@ -2752,13 +2632,13 @@
         <v>23</v>
       </c>
       <c r="Q38" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R38" s="6" t="s">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="S38" s="9">
-        <v>685.71</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" ht="23" customHeight="1">
@@ -2766,22 +2646,22 @@
         <v>22</v>
       </c>
       <c r="B39" s="7">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="C39" s="7">
-        <v>46125</v>
+        <v>46082</v>
       </c>
       <c r="D39" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>23</v>
+        <v>46153</v>
+      </c>
+      <c r="E39" s="7">
+        <v>46097</v>
       </c>
       <c r="F39" s="8">
-        <v>-29</v>
+        <v>-2</v>
       </c>
       <c r="G39" s="8">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>25</v>
@@ -2790,13 +2670,13 @@
         <v>25</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>83</v>
+        <v>31</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="M39" s="6" t="s">
         <v>23</v>
@@ -2811,13 +2691,13 @@
         <v>23</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S39" s="9">
-        <v>53.82</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="40" ht="23" customHeight="1">
@@ -2825,22 +2705,22 @@
         <v>22</v>
       </c>
       <c r="B40" s="7">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="C40" s="7">
-        <v>46146</v>
+        <v>46139</v>
       </c>
       <c r="D40" s="7">
-        <v>46146</v>
+        <v>46132</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F40" s="8">
-        <v>-8</v>
+        <v>-23</v>
       </c>
       <c r="G40" s="8">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>25</v>
@@ -2849,13 +2729,13 @@
         <v>25</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="M40" s="6" t="s">
         <v>23</v>
@@ -2873,10 +2753,10 @@
         <v>23</v>
       </c>
       <c r="R40" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S40" s="9">
-        <v>170</v>
+        <v>450</v>
       </c>
     </row>
     <row r="41" ht="23" customHeight="1">
@@ -2884,22 +2764,22 @@
         <v>22</v>
       </c>
       <c r="B41" s="7">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="C41" s="7">
-        <v>46125</v>
+        <v>46153</v>
       </c>
       <c r="D41" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>23</v>
+        <v>46153</v>
+      </c>
+      <c r="E41" s="7">
+        <v>46119</v>
       </c>
       <c r="F41" s="8">
-        <v>-29</v>
+        <v>-2</v>
       </c>
       <c r="G41" s="8">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>25</v>
@@ -2908,16 +2788,16 @@
         <v>25</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="N41" s="6" t="s">
         <v>28</v>
@@ -2929,13 +2809,13 @@
         <v>23</v>
       </c>
       <c r="Q41" s="6" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="R41" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S41" s="9">
-        <v>250</v>
+        <v>600</v>
       </c>
     </row>
     <row r="42" ht="23" customHeight="1">
@@ -2943,22 +2823,22 @@
         <v>22</v>
       </c>
       <c r="B42" s="7">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="C42" s="7">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D42" s="7">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="E42" s="7">
-        <v>46153</v>
+        <v>46127</v>
       </c>
       <c r="F42" s="8">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="G42" s="8">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>25</v>
@@ -2967,16 +2847,16 @@
         <v>25</v>
       </c>
       <c r="J42" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L42" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="K42" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L42" s="6" t="s">
-        <v>88</v>
-      </c>
       <c r="M42" s="6" t="s">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="N42" s="6" t="s">
         <v>28</v>
@@ -2994,7 +2874,7 @@
         <v>30</v>
       </c>
       <c r="S42" s="9">
-        <v>278.57</v>
+        <v>600</v>
       </c>
     </row>
     <row r="43" ht="23" customHeight="1">
@@ -3005,19 +2885,19 @@
         <v>46153</v>
       </c>
       <c r="C43" s="7">
-        <v>46082</v>
+        <v>46153</v>
       </c>
       <c r="D43" s="7">
         <v>46153</v>
       </c>
       <c r="E43" s="7">
-        <v>46097</v>
+        <v>46119</v>
       </c>
       <c r="F43" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G43" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H43" s="6" t="s">
         <v>25</v>
@@ -3026,16 +2906,16 @@
         <v>25</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>31</v>
+        <v>88</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="N43" s="6" t="s">
         <v>28</v>
@@ -3047,13 +2927,13 @@
         <v>23</v>
       </c>
       <c r="Q43" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R43" s="6" t="s">
         <v>33</v>
       </c>
       <c r="S43" s="9">
-        <v>146.55</v>
+        <v>620</v>
       </c>
     </row>
     <row r="44" ht="23" customHeight="1">
@@ -3070,13 +2950,13 @@
         <v>46153</v>
       </c>
       <c r="E44" s="7">
-        <v>46112</v>
+        <v>46141</v>
       </c>
       <c r="F44" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G44" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>25</v>
@@ -3085,16 +2965,16 @@
         <v>25</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c r="N44" s="6" t="s">
         <v>28</v>
@@ -3112,7 +2992,7 @@
         <v>30</v>
       </c>
       <c r="S44" s="9">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="45" ht="23" customHeight="1">
@@ -3129,13 +3009,13 @@
         <v>46153</v>
       </c>
       <c r="E45" s="7">
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="F45" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G45" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H45" s="6" t="s">
         <v>25</v>
@@ -3150,10 +3030,10 @@
         <v>23</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="N45" s="6" t="s">
         <v>28</v>
@@ -3171,7 +3051,7 @@
         <v>30</v>
       </c>
       <c r="S45" s="9">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="46" ht="23" customHeight="1">
@@ -3188,13 +3068,13 @@
         <v>46153</v>
       </c>
       <c r="E46" s="7">
-        <v>46127</v>
+        <v>46150</v>
       </c>
       <c r="F46" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G46" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>25</v>
@@ -3203,16 +3083,16 @@
         <v>25</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>93</v>
+        <v>23</v>
       </c>
       <c r="N46" s="6" t="s">
         <v>28</v>
@@ -3230,7 +3110,7 @@
         <v>30</v>
       </c>
       <c r="S46" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="47" ht="23" customHeight="1">
@@ -3247,13 +3127,13 @@
         <v>46153</v>
       </c>
       <c r="E47" s="7">
-        <v>46141</v>
+        <v>46127</v>
       </c>
       <c r="F47" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G47" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H47" s="6" t="s">
         <v>25</v>
@@ -3268,7 +3148,7 @@
         <v>23</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="M47" s="6" t="s">
         <v>23</v>
@@ -3289,7 +3169,7 @@
         <v>30</v>
       </c>
       <c r="S47" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="48" ht="23" customHeight="1">
@@ -3306,13 +3186,13 @@
         <v>46153</v>
       </c>
       <c r="E48" s="7">
-        <v>46141</v>
+        <v>46112</v>
       </c>
       <c r="F48" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G48" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>25</v>
@@ -3321,16 +3201,16 @@
         <v>25</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K48" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="N48" s="6" t="s">
         <v>28</v>
@@ -3348,7 +3228,7 @@
         <v>30</v>
       </c>
       <c r="S48" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="49" ht="23" customHeight="1">
@@ -3365,13 +3245,13 @@
         <v>46153</v>
       </c>
       <c r="E49" s="7">
-        <v>46119</v>
+        <v>46112</v>
       </c>
       <c r="F49" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G49" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H49" s="6" t="s">
         <v>25</v>
@@ -3380,16 +3260,16 @@
         <v>25</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>97</v>
+        <v>23</v>
       </c>
       <c r="N49" s="6" t="s">
         <v>28</v>
@@ -3404,10 +3284,10 @@
         <v>39</v>
       </c>
       <c r="R49" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S49" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="50" ht="23" customHeight="1">
@@ -3424,13 +3304,13 @@
         <v>46153</v>
       </c>
       <c r="E50" s="7">
-        <v>46112</v>
+        <v>46092</v>
       </c>
       <c r="F50" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G50" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H50" s="6" t="s">
         <v>25</v>
@@ -3439,13 +3319,13 @@
         <v>25</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M50" s="6" t="s">
         <v>23</v>
@@ -3466,7 +3346,7 @@
         <v>30</v>
       </c>
       <c r="S50" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="51" ht="23" customHeight="1">
@@ -3483,13 +3363,13 @@
         <v>46153</v>
       </c>
       <c r="E51" s="7">
-        <v>46112</v>
+        <v>46119</v>
       </c>
       <c r="F51" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G51" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H51" s="6" t="s">
         <v>25</v>
@@ -3498,16 +3378,16 @@
         <v>25</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K51" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="M51" s="6" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="N51" s="6" t="s">
         <v>28</v>
@@ -3525,7 +3405,7 @@
         <v>30</v>
       </c>
       <c r="S51" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="52" ht="23" customHeight="1">
@@ -3545,10 +3425,10 @@
         <v>46119</v>
       </c>
       <c r="F52" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G52" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>25</v>
@@ -3557,13 +3437,13 @@
         <v>25</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K52" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M52" s="6" t="s">
         <v>23</v>
@@ -3575,7 +3455,7 @@
         <v>28</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q52" s="6" t="s">
         <v>39</v>
@@ -3584,7 +3464,7 @@
         <v>30</v>
       </c>
       <c r="S52" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="53" ht="23" customHeight="1">
@@ -3601,13 +3481,13 @@
         <v>46153</v>
       </c>
       <c r="E53" s="7">
-        <v>46127</v>
+        <v>46119</v>
       </c>
       <c r="F53" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G53" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H53" s="6" t="s">
         <v>25</v>
@@ -3616,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K53" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="M53" s="6" t="s">
         <v>23</v>
@@ -3640,10 +3520,10 @@
         <v>39</v>
       </c>
       <c r="R53" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S53" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="54" ht="23" customHeight="1">
@@ -3660,13 +3540,13 @@
         <v>46153</v>
       </c>
       <c r="E54" s="7">
-        <v>46150</v>
+        <v>46141</v>
       </c>
       <c r="F54" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G54" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H54" s="6" t="s">
         <v>25</v>
@@ -3681,7 +3561,7 @@
         <v>23</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="M54" s="6" t="s">
         <v>23</v>
@@ -3699,10 +3579,10 @@
         <v>39</v>
       </c>
       <c r="R54" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S54" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="55" ht="23" customHeight="1">
@@ -3719,13 +3599,13 @@
         <v>46153</v>
       </c>
       <c r="E55" s="7">
-        <v>46127</v>
+        <v>46092</v>
       </c>
       <c r="F55" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G55" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H55" s="6" t="s">
         <v>25</v>
@@ -3734,13 +3614,13 @@
         <v>25</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K55" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M55" s="6" t="s">
         <v>23</v>
@@ -3761,7 +3641,7 @@
         <v>30</v>
       </c>
       <c r="S55" s="9">
-        <v>650</v>
+        <v>700</v>
       </c>
     </row>
     <row r="56" ht="23" customHeight="1">
@@ -3781,10 +3661,10 @@
         <v>46119</v>
       </c>
       <c r="F56" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G56" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H56" s="6" t="s">
         <v>25</v>
@@ -3793,16 +3673,16 @@
         <v>25</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K56" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="N56" s="6" t="s">
         <v>28</v>
@@ -3811,7 +3691,7 @@
         <v>28</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q56" s="6" t="s">
         <v>39</v>
@@ -3820,7 +3700,7 @@
         <v>30</v>
       </c>
       <c r="S56" s="9">
-        <v>650</v>
+        <v>700</v>
       </c>
     </row>
     <row r="57" ht="23" customHeight="1">
@@ -3828,19 +3708,19 @@
         <v>22</v>
       </c>
       <c r="B57" s="7">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C57" s="7">
-        <v>46153</v>
+        <v>46132</v>
       </c>
       <c r="D57" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E57" s="7">
-        <v>46092</v>
+        <v>46132</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F57" s="8">
-        <v>-1</v>
+        <v>-23</v>
       </c>
       <c r="G57" s="8">
         <v>-1</v>
@@ -3852,16 +3732,16 @@
         <v>25</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K57" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="M57" s="6" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="N57" s="6" t="s">
         <v>28</v>
@@ -3873,13 +3753,13 @@
         <v>23</v>
       </c>
       <c r="Q57" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R57" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S57" s="9">
-        <v>650</v>
+        <v>317.54</v>
       </c>
     </row>
     <row r="58" ht="23" customHeight="1">
@@ -3887,58 +3767,58 @@
         <v>22</v>
       </c>
       <c r="B58" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C58" s="7">
-        <v>46153</v>
+        <v>46082</v>
       </c>
       <c r="D58" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="E58" s="7">
-        <v>46119</v>
+        <v>46097</v>
       </c>
       <c r="F58" s="8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G58" s="8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J58" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K58" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L58" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M58" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N58" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="K58" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L58" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="M58" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N58" s="6" t="s">
-        <v>28</v>
-      </c>
       <c r="O58" s="6" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q58" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R58" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S58" s="9">
-        <v>670</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="59" ht="23" customHeight="1">
@@ -3946,46 +3826,46 @@
         <v>22</v>
       </c>
       <c r="B59" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C59" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="D59" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="E59" s="7">
         <v>46119</v>
       </c>
       <c r="F59" s="8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G59" s="8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K59" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>114</v>
+        <v>48</v>
       </c>
       <c r="M59" s="6" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="N59" s="6" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="O59" s="6" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="P59" s="6" t="s">
         <v>23</v>
@@ -3997,7 +3877,7 @@
         <v>30</v>
       </c>
       <c r="S59" s="9">
-        <v>680</v>
+        <v>600</v>
       </c>
     </row>
     <row r="60" ht="23" customHeight="1">
@@ -4005,46 +3885,46 @@
         <v>22</v>
       </c>
       <c r="B60" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C60" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="D60" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="E60" s="7">
-        <v>46119</v>
+        <v>46112</v>
       </c>
       <c r="F60" s="8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G60" s="8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>32</v>
+        <v>114</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>23</v>
@@ -4053,10 +3933,10 @@
         <v>39</v>
       </c>
       <c r="R60" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S60" s="9">
-        <v>680</v>
+        <v>600</v>
       </c>
     </row>
     <row r="61" ht="23" customHeight="1">
@@ -4064,46 +3944,46 @@
         <v>22</v>
       </c>
       <c r="B61" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C61" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="D61" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="E61" s="7">
-        <v>46141</v>
+        <v>46127</v>
       </c>
       <c r="F61" s="8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G61" s="8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="M61" s="6" t="s">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="N61" s="6" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="P61" s="6" t="s">
         <v>23</v>
@@ -4112,10 +3992,10 @@
         <v>39</v>
       </c>
       <c r="R61" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S61" s="9">
-        <v>680</v>
+        <v>600</v>
       </c>
     </row>
     <row r="62" ht="23" customHeight="1">
@@ -4123,58 +4003,58 @@
         <v>22</v>
       </c>
       <c r="B62" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C62" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="D62" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="E62" s="7">
         <v>46119</v>
       </c>
       <c r="F62" s="8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G62" s="8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q62" s="6" t="s">
         <v>39</v>
       </c>
       <c r="R62" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S62" s="9">
-        <v>700</v>
+        <v>620</v>
       </c>
     </row>
     <row r="63" ht="23" customHeight="1">
@@ -4182,46 +4062,46 @@
         <v>22</v>
       </c>
       <c r="B63" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C63" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="D63" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="E63" s="7">
-        <v>46099</v>
+        <v>46141</v>
       </c>
       <c r="F63" s="8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G63" s="8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="K63" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>120</v>
+        <v>61</v>
       </c>
       <c r="M63" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N63" s="6" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="P63" s="6" t="s">
         <v>23</v>
@@ -4230,10 +4110,10 @@
         <v>39</v>
       </c>
       <c r="R63" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S63" s="9">
-        <v>700</v>
+        <v>620</v>
       </c>
     </row>
     <row r="64" ht="23" customHeight="1">
@@ -4241,46 +4121,46 @@
         <v>22</v>
       </c>
       <c r="B64" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C64" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="D64" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="E64" s="7">
-        <v>46092</v>
+        <v>46141</v>
       </c>
       <c r="F64" s="8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G64" s="8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K64" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="M64" s="6" t="s">
-        <v>23</v>
+        <v>92</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>23</v>
@@ -4292,7 +4172,7 @@
         <v>30</v>
       </c>
       <c r="S64" s="9">
-        <v>700</v>
+        <v>620</v>
       </c>
     </row>
     <row r="65" ht="23" customHeight="1">
@@ -4300,46 +4180,46 @@
         <v>22</v>
       </c>
       <c r="B65" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C65" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="D65" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="E65" s="7">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="F65" s="8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G65" s="8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="K65" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="M65" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N65" s="6" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="O65" s="6" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="P65" s="6" t="s">
         <v>23</v>
@@ -4348,10 +4228,10 @@
         <v>39</v>
       </c>
       <c r="R65" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="S65" s="9">
-        <v>800</v>
+        <v>630</v>
       </c>
     </row>
     <row r="66" ht="23" customHeight="1">
@@ -4359,46 +4239,46 @@
         <v>22</v>
       </c>
       <c r="B66" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C66" s="7">
-        <v>46147</v>
+        <v>46160</v>
       </c>
       <c r="D66" s="7">
-        <v>46147</v>
+        <v>46160</v>
       </c>
       <c r="E66" s="7">
-        <v>46148</v>
+        <v>46127</v>
       </c>
       <c r="F66" s="8">
-        <v>-7</v>
+        <v>5</v>
       </c>
       <c r="G66" s="8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="K66" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="M66" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>23</v>
@@ -4407,10 +4287,10 @@
         <v>39</v>
       </c>
       <c r="R66" s="6" t="s">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="S66" s="9">
-        <v>1028.57</v>
+        <v>630</v>
       </c>
     </row>
     <row r="67" ht="23" customHeight="1">
@@ -4418,58 +4298,58 @@
         <v>22</v>
       </c>
       <c r="B67" s="7">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="C67" s="7">
-        <v>46132</v>
+        <v>46160</v>
       </c>
       <c r="D67" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E67" s="7" t="s">
-        <v>23</v>
+        <v>46160</v>
+      </c>
+      <c r="E67" s="7">
+        <v>46119</v>
       </c>
       <c r="F67" s="8">
-        <v>-22</v>
+        <v>5</v>
       </c>
       <c r="G67" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I67" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="K67" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="N67" s="6" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="O67" s="6" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="P67" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q67" s="6" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="R67" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S67" s="9">
-        <v>317.54</v>
+        <v>630</v>
       </c>
     </row>
     <row r="68" ht="23" customHeight="1">
@@ -4480,19 +4360,19 @@
         <v>46160</v>
       </c>
       <c r="C68" s="7">
-        <v>46082</v>
+        <v>46160</v>
       </c>
       <c r="D68" s="7">
         <v>46160</v>
       </c>
       <c r="E68" s="7">
-        <v>46097</v>
+        <v>46112</v>
       </c>
       <c r="F68" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G68" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H68" s="6" t="s">
         <v>23</v>
@@ -4501,34 +4381,34 @@
         <v>23</v>
       </c>
       <c r="J68" s="6" t="s">
-        <v>31</v>
+        <v>123</v>
       </c>
       <c r="K68" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L68" s="6" t="s">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="M68" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q68" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R68" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S68" s="9">
-        <v>146.55</v>
+        <v>630</v>
       </c>
     </row>
     <row r="69" ht="23" customHeight="1">
@@ -4548,10 +4428,10 @@
         <v>46112</v>
       </c>
       <c r="F69" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G69" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H69" s="6" t="s">
         <v>23</v>
@@ -4560,22 +4440,22 @@
         <v>23</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="K69" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>90</v>
+        <v>37</v>
       </c>
       <c r="M69" s="6" t="s">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c r="N69" s="6" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="O69" s="6" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="P69" s="6" t="s">
         <v>23</v>
@@ -4587,7 +4467,7 @@
         <v>30</v>
       </c>
       <c r="S69" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="70" ht="23" customHeight="1">
@@ -4604,13 +4484,13 @@
         <v>46160</v>
       </c>
       <c r="E70" s="7">
-        <v>46119</v>
+        <v>46092</v>
       </c>
       <c r="F70" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G70" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H70" s="6" t="s">
         <v>23</v>
@@ -4619,22 +4499,22 @@
         <v>23</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K70" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>23</v>
@@ -4646,7 +4526,7 @@
         <v>30</v>
       </c>
       <c r="S70" s="9">
-        <v>600</v>
+        <v>650</v>
       </c>
     </row>
     <row r="71" ht="23" customHeight="1">
@@ -4666,10 +4546,10 @@
         <v>46127</v>
       </c>
       <c r="F71" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G71" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H71" s="6" t="s">
         <v>23</v>
@@ -4678,22 +4558,22 @@
         <v>23</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="K71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="M71" s="6" t="s">
-        <v>93</v>
+        <v>23</v>
       </c>
       <c r="N71" s="6" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="O71" s="6" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="P71" s="6" t="s">
         <v>23</v>
@@ -4705,7 +4585,7 @@
         <v>30</v>
       </c>
       <c r="S71" s="9">
-        <v>600</v>
+        <v>650</v>
       </c>
     </row>
     <row r="72" ht="23" customHeight="1">
@@ -4725,10 +4605,10 @@
         <v>46119</v>
       </c>
       <c r="F72" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G72" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H72" s="6" t="s">
         <v>23</v>
@@ -4737,22 +4617,22 @@
         <v>23</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K72" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>23</v>
@@ -4761,10 +4641,10 @@
         <v>39</v>
       </c>
       <c r="R72" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S72" s="9">
-        <v>620</v>
+        <v>650</v>
       </c>
     </row>
     <row r="73" ht="23" customHeight="1">
@@ -4781,13 +4661,13 @@
         <v>46160</v>
       </c>
       <c r="E73" s="7">
-        <v>46141</v>
+        <v>46153</v>
       </c>
       <c r="F73" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G73" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H73" s="6" t="s">
         <v>23</v>
@@ -4796,22 +4676,22 @@
         <v>23</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="K73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="M73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N73" s="6" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="O73" s="6" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="P73" s="6" t="s">
         <v>23</v>
@@ -4823,7 +4703,7 @@
         <v>30</v>
       </c>
       <c r="S73" s="9">
-        <v>620</v>
+        <v>650</v>
       </c>
     </row>
     <row r="74" ht="23" customHeight="1">
@@ -4840,13 +4720,13 @@
         <v>46160</v>
       </c>
       <c r="E74" s="7">
-        <v>46141</v>
+        <v>46119</v>
       </c>
       <c r="F74" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G74" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H74" s="6" t="s">
         <v>23</v>
@@ -4855,22 +4735,22 @@
         <v>23</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>43</v>
+        <v>131</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>23</v>
@@ -4882,7 +4762,7 @@
         <v>30</v>
       </c>
       <c r="S74" s="9">
-        <v>620</v>
+        <v>670</v>
       </c>
     </row>
     <row r="75" ht="23" customHeight="1">
@@ -4899,13 +4779,13 @@
         <v>46160</v>
       </c>
       <c r="E75" s="7">
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="F75" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G75" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H75" s="6" t="s">
         <v>23</v>
@@ -4914,34 +4794,34 @@
         <v>23</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="K75" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="M75" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N75" s="6" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="O75" s="6" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="P75" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q75" s="6" t="s">
         <v>39</v>
       </c>
       <c r="R75" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S75" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="76" ht="23" customHeight="1">
@@ -4958,13 +4838,13 @@
         <v>46160</v>
       </c>
       <c r="E76" s="7">
-        <v>46127</v>
+        <v>46119</v>
       </c>
       <c r="F76" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G76" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H76" s="6" t="s">
         <v>23</v>
@@ -4973,22 +4853,22 @@
         <v>23</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M76" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>23</v>
@@ -5000,7 +4880,7 @@
         <v>30</v>
       </c>
       <c r="S76" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="77" ht="23" customHeight="1">
@@ -5017,13 +4897,13 @@
         <v>46160</v>
       </c>
       <c r="E77" s="7">
-        <v>46112</v>
+        <v>46119</v>
       </c>
       <c r="F77" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G77" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>23</v>
@@ -5032,22 +4912,22 @@
         <v>23</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="K77" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="M77" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N77" s="6" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="O77" s="6" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="P77" s="6" t="s">
         <v>23</v>
@@ -5056,10 +4936,10 @@
         <v>39</v>
       </c>
       <c r="R77" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S77" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="78" ht="23" customHeight="1">
@@ -5076,13 +4956,13 @@
         <v>46160</v>
       </c>
       <c r="E78" s="7">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="F78" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G78" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H78" s="6" t="s">
         <v>23</v>
@@ -5091,22 +4971,22 @@
         <v>23</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L78" s="6" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="M78" s="6" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>23</v>
@@ -5118,7 +4998,7 @@
         <v>30</v>
       </c>
       <c r="S78" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="79" ht="23" customHeight="1">
@@ -5135,13 +5015,13 @@
         <v>46160</v>
       </c>
       <c r="E79" s="7">
-        <v>46150</v>
+        <v>46092</v>
       </c>
       <c r="F79" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G79" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H79" s="6" t="s">
         <v>23</v>
@@ -5150,22 +5030,22 @@
         <v>23</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="K79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="M79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N79" s="6" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="O79" s="6" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="P79" s="6" t="s">
         <v>23</v>
@@ -5177,7 +5057,7 @@
         <v>30</v>
       </c>
       <c r="S79" s="9">
-        <v>630</v>
+        <v>700</v>
       </c>
     </row>
     <row r="80" ht="23" customHeight="1">
@@ -5194,13 +5074,13 @@
         <v>46160</v>
       </c>
       <c r="E80" s="7">
-        <v>46153</v>
+        <v>46099</v>
       </c>
       <c r="F80" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G80" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H80" s="6" t="s">
         <v>23</v>
@@ -5209,22 +5089,22 @@
         <v>23</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L80" s="6" t="s">
-        <v>88</v>
+        <v>138</v>
       </c>
       <c r="M80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>23</v>
@@ -5233,10 +5113,10 @@
         <v>39</v>
       </c>
       <c r="R80" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S80" s="9">
-        <v>650</v>
+        <v>700</v>
       </c>
     </row>
     <row r="81" ht="23" customHeight="1">
@@ -5253,13 +5133,13 @@
         <v>46160</v>
       </c>
       <c r="E81" s="7">
-        <v>46092</v>
+        <v>46119</v>
       </c>
       <c r="F81" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G81" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H81" s="6" t="s">
         <v>23</v>
@@ -5268,25 +5148,25 @@
         <v>23</v>
       </c>
       <c r="J81" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="M81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N81" s="6" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="O81" s="6" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="P81" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q81" s="6" t="s">
         <v>39</v>
@@ -5295,2190 +5175,66 @@
         <v>30</v>
       </c>
       <c r="S81" s="9">
-        <v>650</v>
+        <v>700</v>
       </c>
     </row>
     <row r="82" ht="23" customHeight="1">
-      <c r="A82" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B82" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C82" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D82" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E82" s="7">
-        <v>46127</v>
-      </c>
-      <c r="F82" s="8">
-        <v>6</v>
-      </c>
-      <c r="G82" s="8">
-        <v>6</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I82" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J82" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="K82" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L82" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="M82" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N82" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O82" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P82" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q82" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R82" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S82" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="83" ht="23" customHeight="1">
-      <c r="A83" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B83" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C83" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D83" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E83" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F83" s="8">
-        <v>6</v>
-      </c>
-      <c r="G83" s="8">
-        <v>6</v>
-      </c>
-      <c r="H83" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I83" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J83" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="K83" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L83" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="M83" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="N83" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O83" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P83" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q83" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R83" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S83" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="84" ht="23" customHeight="1">
-      <c r="A84" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B84" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C84" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D84" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E84" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F84" s="8">
-        <v>6</v>
-      </c>
-      <c r="G84" s="8">
-        <v>6</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I84" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J84" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="K84" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L84" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="M84" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N84" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O84" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P84" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q84" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R84" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S84" s="9">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="85" ht="23" customHeight="1">
-      <c r="A85" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B85" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C85" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D85" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E85" s="7">
-        <v>46113</v>
-      </c>
-      <c r="F85" s="8">
-        <v>6</v>
-      </c>
-      <c r="G85" s="8">
-        <v>6</v>
-      </c>
-      <c r="H85" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I85" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J85" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K85" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L85" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="M85" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="N85" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O85" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P85" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q85" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R85" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S85" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="86" ht="23" customHeight="1">
-      <c r="A86" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B86" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C86" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D86" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E86" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F86" s="8">
-        <v>6</v>
-      </c>
-      <c r="G86" s="8">
-        <v>6</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I86" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J86" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="K86" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L86" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="M86" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N86" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O86" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P86" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q86" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R86" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S86" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="87" ht="23" customHeight="1">
-      <c r="A87" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B87" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C87" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D87" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E87" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F87" s="8">
-        <v>6</v>
-      </c>
-      <c r="G87" s="8">
-        <v>6</v>
-      </c>
-      <c r="H87" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I87" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J87" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="K87" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L87" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="M87" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N87" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O87" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P87" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q87" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R87" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="S87" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="88" ht="23" customHeight="1">
-      <c r="A88" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B88" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C88" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D88" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E88" s="7">
-        <v>46141</v>
-      </c>
-      <c r="F88" s="8">
-        <v>6</v>
-      </c>
-      <c r="G88" s="8">
-        <v>6</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I88" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J88" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="K88" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L88" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="M88" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N88" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O88" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P88" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q88" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R88" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="S88" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="89" ht="23" customHeight="1">
-      <c r="A89" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B89" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C89" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D89" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E89" s="7">
-        <v>46092</v>
-      </c>
-      <c r="F89" s="8">
-        <v>6</v>
-      </c>
-      <c r="G89" s="8">
-        <v>6</v>
-      </c>
-      <c r="H89" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I89" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J89" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="K89" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L89" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="M89" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N89" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O89" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P89" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q89" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R89" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S89" s="9">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="90" ht="23" customHeight="1">
-      <c r="A90" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B90" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C90" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D90" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E90" s="7">
-        <v>46099</v>
-      </c>
-      <c r="F90" s="8">
-        <v>6</v>
-      </c>
-      <c r="G90" s="8">
-        <v>6</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I90" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J90" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="K90" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L90" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="M90" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N90" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O90" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P90" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q90" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R90" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="S90" s="9">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="91" ht="23" customHeight="1">
-      <c r="A91" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B91" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C91" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D91" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E91" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F91" s="8">
-        <v>6</v>
-      </c>
-      <c r="G91" s="8">
-        <v>6</v>
-      </c>
-      <c r="H91" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I91" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J91" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="K91" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L91" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="M91" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N91" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O91" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P91" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q91" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R91" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S91" s="9">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="92" ht="23" customHeight="1">
-      <c r="A92" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B92" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C92" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D92" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E92" s="7">
-        <v>46148</v>
-      </c>
-      <c r="F92" s="8">
-        <v>6</v>
-      </c>
-      <c r="G92" s="8">
-        <v>6</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I92" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J92" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="K92" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L92" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="M92" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N92" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O92" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P92" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q92" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R92" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="S92" s="9">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="93" ht="23" customHeight="1">
-      <c r="A93" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B93" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C93" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D93" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E93" s="7">
-        <v>46148</v>
-      </c>
-      <c r="F93" s="8">
-        <v>6</v>
-      </c>
-      <c r="G93" s="8">
-        <v>6</v>
-      </c>
-      <c r="H93" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I93" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J93" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="K93" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L93" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="M93" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N93" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O93" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P93" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q93" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R93" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="S93" s="9">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="94" ht="23" customHeight="1">
-      <c r="A94" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B94" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C94" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D94" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E94" s="7">
-        <v>46148</v>
-      </c>
-      <c r="F94" s="8">
-        <v>6</v>
-      </c>
-      <c r="G94" s="8">
-        <v>6</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I94" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J94" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="K94" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L94" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="M94" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N94" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O94" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P94" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q94" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R94" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="S94" s="9">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="95" ht="23" customHeight="1">
-      <c r="A95" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B95" s="7">
-        <v>46161</v>
-      </c>
-      <c r="C95" s="7">
-        <v>46113</v>
-      </c>
-      <c r="D95" s="7">
-        <v>46150</v>
-      </c>
-      <c r="E95" s="7">
-        <v>46149</v>
-      </c>
-      <c r="F95" s="8">
-        <v>-4</v>
-      </c>
-      <c r="G95" s="8">
-        <v>7</v>
-      </c>
-      <c r="H95" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I95" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J95" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="K95" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L95" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="M95" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="N95" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="O95" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P95" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q95" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R95" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S95" s="9">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="96" ht="23" customHeight="1">
-      <c r="A96" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B96" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C96" s="7">
-        <v>46082</v>
-      </c>
-      <c r="D96" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E96" s="7">
-        <v>46097</v>
-      </c>
-      <c r="F96" s="8">
-        <v>13</v>
-      </c>
-      <c r="G96" s="8">
-        <v>13</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I96" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J96" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="K96" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L96" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="M96" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N96" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O96" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P96" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q96" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="R96" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="S96" s="9">
-        <v>146.55</v>
-      </c>
-    </row>
-    <row r="97" ht="23" customHeight="1">
-      <c r="A97" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B97" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C97" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D97" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E97" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F97" s="8">
-        <v>13</v>
-      </c>
-      <c r="G97" s="8">
-        <v>13</v>
-      </c>
-      <c r="H97" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I97" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J97" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="K97" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L97" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="M97" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="N97" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O97" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P97" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q97" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R97" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S97" s="9">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="98" ht="23" customHeight="1">
-      <c r="A98" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B98" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C98" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D98" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E98" s="7">
-        <v>46141</v>
-      </c>
-      <c r="F98" s="8">
-        <v>13</v>
-      </c>
-      <c r="G98" s="8">
-        <v>13</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I98" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J98" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="K98" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L98" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="M98" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N98" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O98" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P98" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q98" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R98" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S98" s="9">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="99" ht="23" customHeight="1">
-      <c r="A99" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B99" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C99" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D99" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E99" s="7">
-        <v>46141</v>
-      </c>
-      <c r="F99" s="8">
-        <v>13</v>
-      </c>
-      <c r="G99" s="8">
-        <v>13</v>
-      </c>
-      <c r="H99" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I99" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J99" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="K99" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L99" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="M99" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="N99" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O99" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P99" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q99" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R99" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S99" s="9">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="100" ht="23" customHeight="1">
-      <c r="A100" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B100" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C100" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D100" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E100" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F100" s="8">
-        <v>13</v>
-      </c>
-      <c r="G100" s="8">
-        <v>13</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I100" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J100" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="K100" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L100" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="M100" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="N100" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O100" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P100" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q100" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R100" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="S100" s="9">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="101" ht="23" customHeight="1">
-      <c r="A101" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B101" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C101" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D101" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E101" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F101" s="8">
-        <v>13</v>
-      </c>
-      <c r="G101" s="8">
-        <v>13</v>
-      </c>
-      <c r="H101" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I101" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J101" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="K101" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L101" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="M101" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N101" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O101" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P101" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q101" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R101" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S101" s="9">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="102" ht="23" customHeight="1">
-      <c r="A102" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B102" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C102" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D102" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E102" s="7">
-        <v>46150</v>
-      </c>
-      <c r="F102" s="8">
-        <v>13</v>
-      </c>
-      <c r="G102" s="8">
-        <v>13</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I102" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J102" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="K102" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L102" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="M102" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N102" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O102" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P102" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q102" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R102" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S102" s="9">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="103" ht="23" customHeight="1">
-      <c r="A103" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B103" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C103" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D103" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E103" s="7">
-        <v>46153</v>
-      </c>
-      <c r="F103" s="8">
-        <v>13</v>
-      </c>
-      <c r="G103" s="8">
-        <v>13</v>
-      </c>
-      <c r="H103" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I103" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J103" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="K103" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L103" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="M103" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N103" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O103" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P103" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q103" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R103" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S103" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="104" ht="23" customHeight="1">
-      <c r="A104" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B104" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C104" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D104" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E104" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F104" s="8">
-        <v>13</v>
-      </c>
-      <c r="G104" s="8">
-        <v>13</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I104" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J104" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="K104" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L104" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="M104" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="N104" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O104" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P104" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q104" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R104" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S104" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="105" ht="23" customHeight="1">
-      <c r="A105" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B105" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C105" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D105" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E105" s="7">
-        <v>46127</v>
-      </c>
-      <c r="F105" s="8">
-        <v>13</v>
-      </c>
-      <c r="G105" s="8">
-        <v>13</v>
-      </c>
-      <c r="H105" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I105" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J105" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="K105" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L105" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="M105" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N105" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O105" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P105" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q105" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R105" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S105" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="106" ht="23" customHeight="1">
-      <c r="A106" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B106" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C106" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D106" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E106" s="7">
-        <v>46092</v>
-      </c>
-      <c r="F106" s="8">
-        <v>13</v>
-      </c>
-      <c r="G106" s="8">
-        <v>13</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I106" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J106" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="K106" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L106" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="M106" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N106" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O106" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P106" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q106" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R106" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S106" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="107" ht="23" customHeight="1">
-      <c r="A107" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B107" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C107" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D107" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E107" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F107" s="8">
-        <v>13</v>
-      </c>
-      <c r="G107" s="8">
-        <v>13</v>
-      </c>
-      <c r="H107" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I107" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J107" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="K107" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L107" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="M107" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N107" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O107" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P107" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q107" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R107" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S107" s="9">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="108" ht="23" customHeight="1">
-      <c r="A108" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B108" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C108" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D108" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E108" s="7">
-        <v>46113</v>
-      </c>
-      <c r="F108" s="8">
-        <v>13</v>
-      </c>
-      <c r="G108" s="8">
-        <v>13</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I108" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J108" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="K108" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L108" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="M108" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="N108" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O108" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P108" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q108" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R108" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S108" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="109" ht="23" customHeight="1">
-      <c r="A109" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B109" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C109" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D109" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E109" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F109" s="8">
-        <v>13</v>
-      </c>
-      <c r="G109" s="8">
-        <v>13</v>
-      </c>
-      <c r="H109" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I109" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J109" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="K109" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L109" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="M109" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N109" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O109" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P109" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q109" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R109" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S109" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="110" ht="23" customHeight="1">
-      <c r="A110" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B110" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C110" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D110" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E110" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F110" s="8">
-        <v>13</v>
-      </c>
-      <c r="G110" s="8">
-        <v>13</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I110" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J110" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="K110" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L110" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="M110" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N110" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O110" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P110" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q110" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R110" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="S110" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="111" ht="23" customHeight="1">
-      <c r="A111" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B111" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C111" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D111" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E111" s="7">
-        <v>46141</v>
-      </c>
-      <c r="F111" s="8">
-        <v>13</v>
-      </c>
-      <c r="G111" s="8">
-        <v>13</v>
-      </c>
-      <c r="H111" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I111" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J111" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="K111" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L111" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="M111" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N111" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O111" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P111" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q111" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R111" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="S111" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="112" ht="23" customHeight="1">
-      <c r="A112" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B112" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C112" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D112" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E112" s="7">
-        <v>46099</v>
-      </c>
-      <c r="F112" s="8">
-        <v>13</v>
-      </c>
-      <c r="G112" s="8">
-        <v>13</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I112" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J112" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K112" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L112" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="M112" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N112" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O112" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P112" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q112" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R112" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="S112" s="9">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="113" ht="23" customHeight="1">
-      <c r="A113" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B113" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C113" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D113" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E113" s="7">
-        <v>46148</v>
-      </c>
-      <c r="F113" s="8">
-        <v>13</v>
-      </c>
-      <c r="G113" s="8">
-        <v>13</v>
-      </c>
-      <c r="H113" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I113" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J113" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="K113" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L113" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="M113" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N113" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O113" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P113" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q113" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R113" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="S113" s="9">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="114" ht="23" customHeight="1">
-      <c r="A114" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B114" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C114" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D114" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E114" s="7">
-        <v>46148</v>
-      </c>
-      <c r="F114" s="8">
-        <v>13</v>
-      </c>
-      <c r="G114" s="8">
-        <v>13</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I114" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J114" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="K114" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L114" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="M114" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N114" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O114" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P114" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q114" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R114" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="S114" s="9">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="115" ht="23" customHeight="1">
-      <c r="A115" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B115" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C115" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D115" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E115" s="7">
-        <v>46148</v>
-      </c>
-      <c r="F115" s="8">
-        <v>13</v>
-      </c>
-      <c r="G115" s="8">
-        <v>13</v>
-      </c>
-      <c r="H115" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I115" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J115" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="K115" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L115" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="M115" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N115" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O115" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P115" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q115" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R115" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="S115" s="9">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="116" ht="23" customHeight="1">
-      <c r="A116" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B116" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C116" s="7">
-        <v>46113</v>
-      </c>
-      <c r="D116" s="7">
-        <v>46150</v>
-      </c>
-      <c r="E116" s="7">
-        <v>46149</v>
-      </c>
-      <c r="F116" s="8">
-        <v>-4</v>
-      </c>
-      <c r="G116" s="8">
-        <v>13</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I116" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J116" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="K116" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L116" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="M116" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="N116" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="O116" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P116" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q116" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R116" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S116" s="9">
-        <v>4400</v>
-      </c>
-    </row>
-    <row r="117" ht="23" customHeight="1">
-      <c r="A117" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B117" s="7">
-        <v>46172</v>
-      </c>
-      <c r="C117" s="7">
-        <v>45930</v>
-      </c>
-      <c r="D117" s="7">
-        <v>46172</v>
-      </c>
-      <c r="E117" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F117" s="8">
-        <v>18</v>
-      </c>
-      <c r="G117" s="8">
-        <v>18</v>
-      </c>
-      <c r="H117" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I117" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J117" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="K117" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L117" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="M117" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N117" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O117" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P117" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q117" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R117" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="S117" s="9">
-        <v>185.5</v>
-      </c>
-    </row>
-    <row r="118" ht="23" customHeight="1">
-      <c r="A118" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B118" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C118" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D118" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E118" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F118" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G118" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H118" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I118" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J118" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="K118" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="L118" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M118" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="N118" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="O118" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="P118" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q118" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="R118" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="S118" s="13">
-        <f>SUM(S6:S117)</f>
+      <c r="A82" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B82" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C82" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D82" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E82" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F82" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G82" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H82" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I82" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J82" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K82" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L82" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M82" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="N82" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="O82" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="P82" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q82" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="R82" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S82" s="13">
+        <f>SUM(S6:S81)</f>
       </c>
     </row>
   </sheetData>

--- a/docx_templates/CONTAS-A-RECEBER.xlsx
+++ b/docx_templates/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$76</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$95</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -36,11 +36,11 @@
         <color rgb="FF808080"/>
         <sz val="11"/>
       </rPr>
-      <t>Data Inicial: 01/08/2025, Data Final: 18/05/2026, Conta de Recebimento: 1.0 [OFICIAL] SICREDI | BANCO GESTOR</t>
+      <t>Data Inicial: 01/08/2025, Data Final: 31/05/2026, Conta de Recebimento: 1.0 [OFICIAL] SICREDI | BANCO GESTOR</t>
     </r>
   </si>
   <si>
-    <t>Relatório exportado em quarta-feira, 13 de maio de 2026 por KAROL MEDEIROS</t>
+    <t>Relatório exportado em quinta-feira, 14 de maio de 2026 por KAROL MEDEIROS</t>
   </si>
   <si>
     <t>Conta de Recebimento</t>
@@ -241,217 +241,277 @@
     <t>MARIO EWERTON CANDIDO DE SOUZA</t>
   </si>
   <si>
+    <t>FA-11587</t>
+  </si>
+  <si>
+    <t>JACKSON CASSIANO VERISSIMO</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
+  </si>
+  <si>
+    <t>FA-11114</t>
+  </si>
+  <si>
+    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
+  </si>
+  <si>
+    <t>FA-11355</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
+    <t>FA-11496</t>
+  </si>
+  <si>
+    <t>ANDRE CAVALCANTI DA FE</t>
+  </si>
+  <si>
+    <t>FA-11618</t>
+  </si>
+  <si>
+    <t>DANILO DE ALMEIDA TORRES</t>
+  </si>
+  <si>
+    <t>VENCIDO ACIMA DE 90 DIAS</t>
+  </si>
+  <si>
+    <t>ND-10427</t>
+  </si>
+  <si>
+    <t>FA-11497</t>
+  </si>
+  <si>
+    <t>FA-11471</t>
+  </si>
+  <si>
+    <t>FA-11522</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>FA-11557</t>
+  </si>
+  <si>
+    <t>FA-11556</t>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
+  </si>
+  <si>
+    <t>FA-11476</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>FA-11523</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11399</t>
+  </si>
+  <si>
+    <t>FA-11615</t>
+  </si>
+  <si>
+    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11278</t>
+  </si>
+  <si>
+    <t>FELIPE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11473</t>
+  </si>
+  <si>
+    <t>FA-11475</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>FA-11478</t>
+  </si>
+  <si>
+    <t>FA-11558</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11267</t>
+  </si>
+  <si>
+    <t>ANNY KATARINA ACIOLE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11472</t>
+  </si>
+  <si>
     <t>FA-11614</t>
   </si>
   <si>
-    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11587</t>
-  </si>
-  <si>
-    <t>JACKSON CASSIANO VERISSIMO</t>
-  </si>
-  <si>
-    <t>LUZ DIVINA LTDA</t>
-  </si>
-  <si>
-    <t>FA-11114</t>
-  </si>
-  <si>
-    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
-  </si>
-  <si>
-    <t>FA-11355</t>
-  </si>
-  <si>
-    <t>RICARDO ARAUJO DE MIRANDA</t>
-  </si>
-  <si>
-    <t>FA-11496</t>
-  </si>
-  <si>
-    <t>ANDRE CAVALCANTI DA FE</t>
-  </si>
-  <si>
-    <t>FA-11618</t>
-  </si>
-  <si>
-    <t>DANILO DE ALMEIDA TORRES</t>
-  </si>
-  <si>
-    <t>VENCIDO ACIMA DE 90 DIAS</t>
-  </si>
-  <si>
-    <t>ND-10427</t>
-  </si>
-  <si>
-    <t>FA-11497</t>
-  </si>
-  <si>
-    <t>FA-11471</t>
-  </si>
-  <si>
-    <t>FA-11522</t>
-  </si>
-  <si>
-    <t>ROBERTO MURATORI</t>
-  </si>
-  <si>
-    <t>FA-11476</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>FA-11557</t>
-  </si>
-  <si>
-    <t>FA-11556</t>
-  </si>
-  <si>
-    <t>DIEGO TAYAO DANTAS</t>
-  </si>
-  <si>
-    <t>FA-11615</t>
-  </si>
-  <si>
-    <t>FA-11523</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11398</t>
+    <t>FA-11453</t>
+  </si>
+  <si>
+    <t>A VENCER</t>
+  </si>
+  <si>
+    <t>FA-11400</t>
+  </si>
+  <si>
+    <t>JOZILDO TARQUINO DE BRITO</t>
+  </si>
+  <si>
+    <t>FA-11474</t>
+  </si>
+  <si>
+    <t>FA-11525</t>
+  </si>
+  <si>
+    <t>FA-11559</t>
+  </si>
+  <si>
+    <t>FA-11560</t>
+  </si>
+  <si>
+    <t>FA-11481</t>
+  </si>
+  <si>
+    <t>FA-11401</t>
   </si>
   <si>
     <t>ANA FLORIPES CARVALHO DA CUNHA</t>
   </si>
   <si>
-    <t>FA-11399</t>
-  </si>
-  <si>
-    <t>FA-11278</t>
-  </si>
-  <si>
-    <t>FELIPE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11473</t>
-  </si>
-  <si>
-    <t>FA-11475</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
-    <t>FA-11478</t>
-  </si>
-  <si>
-    <t>FA-11558</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11267</t>
-  </si>
-  <si>
-    <t>ANNY KATARINA ACIOLE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11472</t>
-  </si>
-  <si>
-    <t>FA-11453</t>
-  </si>
-  <si>
-    <t>A VENCER</t>
-  </si>
-  <si>
-    <t>FA-11474</t>
-  </si>
-  <si>
-    <t>FA-11400</t>
-  </si>
-  <si>
-    <t>JOZILDO TARQUINO DE BRITO</t>
-  </si>
-  <si>
-    <t>FA-11525</t>
-  </si>
-  <si>
-    <t>FA-11481</t>
-  </si>
-  <si>
-    <t>FA-11559</t>
-  </si>
-  <si>
-    <t>FA-11560</t>
+    <t>FA-11402</t>
+  </si>
+  <si>
+    <t>FA-11493</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11526</t>
   </si>
   <si>
     <t>FA-11616</t>
   </si>
   <si>
-    <t>FA-11526</t>
-  </si>
-  <si>
-    <t>FA-11493</t>
-  </si>
-  <si>
-    <t>ROSSILY PEREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11401</t>
-  </si>
-  <si>
-    <t>FA-11402</t>
+    <t>FA-11620</t>
+  </si>
+  <si>
+    <t>FA-11503</t>
+  </si>
+  <si>
+    <t>WESCLY JEAN DE MEDEIROS</t>
   </si>
   <si>
     <t>FA-11279</t>
   </si>
   <si>
-    <t>FA-11503</t>
-  </si>
-  <si>
-    <t>WESCLY JEAN DE MEDEIROS</t>
-  </si>
-  <si>
     <t>FA-11482</t>
   </si>
   <si>
-    <t>FA-11620</t>
-  </si>
-  <si>
     <t>FA-11433</t>
   </si>
   <si>
     <t>RAYANE ROBERTA DA SILVA</t>
   </si>
   <si>
+    <t>FA-11483</t>
+  </si>
+  <si>
+    <t>FA-11484</t>
+  </si>
+  <si>
+    <t>FA-11411</t>
+  </si>
+  <si>
     <t>FA-11561</t>
   </si>
   <si>
-    <t>FA-11483</t>
-  </si>
-  <si>
-    <t>FA-11484</t>
-  </si>
-  <si>
-    <t>FA-11411</t>
+    <t>FA-11479</t>
+  </si>
+  <si>
+    <t>FA-11328</t>
+  </si>
+  <si>
+    <t>MAICON LOPES SILVA</t>
   </si>
   <si>
     <t>FA-11268</t>
   </si>
   <si>
-    <t>FA-11328</t>
-  </si>
-  <si>
-    <t>MAICON LOPES SILVA</t>
-  </si>
-  <si>
-    <t>FA-11479</t>
+    <t>FA-11611</t>
+  </si>
+  <si>
+    <t>M&amp;S DO TRABALHO</t>
+  </si>
+  <si>
+    <t>FA-11480</t>
+  </si>
+  <si>
+    <t>FA-11562</t>
+  </si>
+  <si>
+    <t>FA-11563</t>
+  </si>
+  <si>
+    <t>FA-11487</t>
+  </si>
+  <si>
+    <t>FA-11494</t>
+  </si>
+  <si>
+    <t>FA-11617</t>
+  </si>
+  <si>
+    <t>FA-11621</t>
+  </si>
+  <si>
+    <t>FA-11504</t>
+  </si>
+  <si>
+    <t>FA-11488</t>
+  </si>
+  <si>
+    <t>FA-11280</t>
+  </si>
+  <si>
+    <t>FA-11434</t>
+  </si>
+  <si>
+    <t>FA-11489</t>
+  </si>
+  <si>
+    <t>FA-11491</t>
+  </si>
+  <si>
+    <t>FA-11412</t>
+  </si>
+  <si>
+    <t>FA-11564</t>
+  </si>
+  <si>
+    <t>FA-11329</t>
+  </si>
+  <si>
+    <t>FA-11613</t>
+  </si>
+  <si>
+    <t>SEGCOMP</t>
+  </si>
+  <si>
+    <t>SEGCOMP TECNOLOGIA LTDA</t>
   </si>
 </sst>
 </file>
@@ -594,7 +654,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S82"/>
+  <dimension ref="A1:S101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.13657760620117" customWidth="1" style="1"/>
@@ -711,10 +771,10 @@
         <v>23</v>
       </c>
       <c r="F6" s="8">
-        <v>-37</v>
+        <v>-38</v>
       </c>
       <c r="G6" s="8">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>24</v>
@@ -770,13 +830,13 @@
         <v>23</v>
       </c>
       <c r="F7" s="8">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="G7" s="8">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>25</v>
@@ -829,10 +889,10 @@
         <v>23</v>
       </c>
       <c r="F8" s="8">
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="G8" s="8">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>24</v>
@@ -888,13 +948,13 @@
         <v>23</v>
       </c>
       <c r="F9" s="8">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="G9" s="8">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>25</v>
@@ -947,10 +1007,10 @@
         <v>46127</v>
       </c>
       <c r="F10" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="G10" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>25</v>
@@ -1006,10 +1066,10 @@
         <v>46097</v>
       </c>
       <c r="F11" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="G11" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>25</v>
@@ -1065,10 +1125,10 @@
         <v>23</v>
       </c>
       <c r="F12" s="8">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="G12" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>25</v>
@@ -1124,10 +1184,10 @@
         <v>23</v>
       </c>
       <c r="F13" s="8">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="G13" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>25</v>
@@ -1183,13 +1243,13 @@
         <v>23</v>
       </c>
       <c r="F14" s="8">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="G14" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>25</v>
@@ -1242,10 +1302,10 @@
         <v>23</v>
       </c>
       <c r="F15" s="8">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="G15" s="8">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>25</v>
@@ -1301,10 +1361,10 @@
         <v>46141</v>
       </c>
       <c r="F16" s="8">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="G16" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>25</v>
@@ -1360,10 +1420,10 @@
         <v>23</v>
       </c>
       <c r="F17" s="8">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="G17" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>25</v>
@@ -1419,10 +1479,10 @@
         <v>23</v>
       </c>
       <c r="F18" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G18" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>25</v>
@@ -1478,13 +1538,13 @@
         <v>23</v>
       </c>
       <c r="F19" s="8">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="G19" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>25</v>
@@ -1537,10 +1597,10 @@
         <v>46097</v>
       </c>
       <c r="F20" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G20" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>25</v>
@@ -1596,10 +1656,10 @@
         <v>23</v>
       </c>
       <c r="F21" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="G21" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>25</v>
@@ -1655,10 +1715,10 @@
         <v>23</v>
       </c>
       <c r="F22" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="G22" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>25</v>
@@ -1714,10 +1774,10 @@
         <v>23</v>
       </c>
       <c r="F23" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G23" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>25</v>
@@ -1773,10 +1833,10 @@
         <v>23</v>
       </c>
       <c r="F24" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="G24" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>25</v>
@@ -1832,10 +1892,10 @@
         <v>46119</v>
       </c>
       <c r="F25" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G25" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>25</v>
@@ -1891,10 +1951,10 @@
         <v>46141</v>
       </c>
       <c r="F26" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G26" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>25</v>
@@ -1950,10 +2010,10 @@
         <v>46112</v>
       </c>
       <c r="F27" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G27" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>25</v>
@@ -2009,10 +2069,10 @@
         <v>46119</v>
       </c>
       <c r="F28" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G28" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>25</v>
@@ -2068,10 +2128,10 @@
         <v>23</v>
       </c>
       <c r="F29" s="8">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="G29" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>25</v>
@@ -2127,10 +2187,10 @@
         <v>46119</v>
       </c>
       <c r="F30" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G30" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>25</v>
@@ -2186,10 +2246,10 @@
         <v>23</v>
       </c>
       <c r="F31" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="G31" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>25</v>
@@ -2236,19 +2296,19 @@
         <v>46149</v>
       </c>
       <c r="C32" s="7">
-        <v>46146</v>
+        <v>46142</v>
       </c>
       <c r="D32" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>23</v>
+        <v>46142</v>
+      </c>
+      <c r="E32" s="7">
+        <v>46148</v>
       </c>
       <c r="F32" s="8">
-        <v>-9</v>
+        <v>-14</v>
       </c>
       <c r="G32" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>25</v>
@@ -2278,13 +2338,13 @@
         <v>23</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="S32" s="9">
-        <v>380</v>
+        <v>685.71</v>
       </c>
     </row>
     <row r="33" ht="23" customHeight="1">
@@ -2292,37 +2352,37 @@
         <v>22</v>
       </c>
       <c r="B33" s="7">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="C33" s="7">
-        <v>46142</v>
+        <v>46125</v>
       </c>
       <c r="D33" s="7">
-        <v>46142</v>
-      </c>
-      <c r="E33" s="7">
-        <v>46148</v>
+        <v>46125</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F33" s="8">
-        <v>-13</v>
+        <v>-31</v>
       </c>
       <c r="G33" s="8">
         <v>-6</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I33" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M33" s="6" t="s">
         <v>23</v>
@@ -2337,13 +2397,13 @@
         <v>23</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="S33" s="9">
-        <v>685.71</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="34" ht="23" customHeight="1">
@@ -2354,19 +2414,19 @@
         <v>46150</v>
       </c>
       <c r="C34" s="7">
-        <v>46125</v>
+        <v>46146</v>
       </c>
       <c r="D34" s="7">
-        <v>46125</v>
+        <v>46146</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F34" s="8">
-        <v>-30</v>
+        <v>-10</v>
       </c>
       <c r="G34" s="8">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>25</v>
@@ -2402,7 +2462,7 @@
         <v>30</v>
       </c>
       <c r="S34" s="9">
-        <v>53.82</v>
+        <v>170</v>
       </c>
     </row>
     <row r="35" ht="23" customHeight="1">
@@ -2413,22 +2473,22 @@
         <v>46150</v>
       </c>
       <c r="C35" s="7">
-        <v>46146</v>
+        <v>46125</v>
       </c>
       <c r="D35" s="7">
-        <v>46146</v>
+        <v>46125</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F35" s="8">
-        <v>-9</v>
+        <v>-31</v>
       </c>
       <c r="G35" s="8">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I35" s="6" t="s">
         <v>25</v>
@@ -2458,10 +2518,10 @@
         <v>23</v>
       </c>
       <c r="R35" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S35" s="9">
-        <v>170</v>
+        <v>250</v>
       </c>
     </row>
     <row r="36" ht="23" customHeight="1">
@@ -2472,19 +2532,19 @@
         <v>46150</v>
       </c>
       <c r="C36" s="7">
-        <v>46125</v>
+        <v>46150</v>
       </c>
       <c r="D36" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>23</v>
+        <v>46150</v>
+      </c>
+      <c r="E36" s="7">
+        <v>46153</v>
       </c>
       <c r="F36" s="8">
-        <v>-30</v>
+        <v>-6</v>
       </c>
       <c r="G36" s="8">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>25</v>
@@ -2514,13 +2574,13 @@
         <v>23</v>
       </c>
       <c r="Q36" s="6" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="R36" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S36" s="9">
-        <v>250</v>
+        <v>278.57</v>
       </c>
     </row>
     <row r="37" ht="23" customHeight="1">
@@ -2528,37 +2588,37 @@
         <v>22</v>
       </c>
       <c r="B37" s="7">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="C37" s="7">
-        <v>46150</v>
+        <v>45901</v>
       </c>
       <c r="D37" s="7">
-        <v>46150</v>
-      </c>
-      <c r="E37" s="7">
-        <v>46153</v>
+        <v>45938</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F37" s="8">
-        <v>-5</v>
+        <v>-218</v>
       </c>
       <c r="G37" s="8">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="I37" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>23</v>
@@ -2573,13 +2633,13 @@
         <v>23</v>
       </c>
       <c r="Q37" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R37" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S37" s="9">
-        <v>278.57</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" ht="23" customHeight="1">
@@ -2590,34 +2650,34 @@
         <v>46153</v>
       </c>
       <c r="C38" s="7">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="D38" s="7">
-        <v>45938</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>23</v>
+        <v>46153</v>
+      </c>
+      <c r="E38" s="7">
+        <v>46097</v>
       </c>
       <c r="F38" s="8">
-        <v>-217</v>
+        <v>-3</v>
       </c>
       <c r="G38" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="I38" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>83</v>
+        <v>31</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>23</v>
@@ -2632,13 +2692,13 @@
         <v>23</v>
       </c>
       <c r="Q38" s="6" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="R38" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S38" s="9">
-        <v>30</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="39" ht="23" customHeight="1">
@@ -2649,19 +2709,19 @@
         <v>46153</v>
       </c>
       <c r="C39" s="7">
-        <v>46082</v>
+        <v>46139</v>
       </c>
       <c r="D39" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E39" s="7">
-        <v>46097</v>
+        <v>46132</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F39" s="8">
-        <v>-2</v>
+        <v>-24</v>
       </c>
       <c r="G39" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>25</v>
@@ -2670,13 +2730,13 @@
         <v>25</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="M39" s="6" t="s">
         <v>23</v>
@@ -2691,13 +2751,13 @@
         <v>23</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="R39" s="6" t="s">
         <v>33</v>
       </c>
       <c r="S39" s="9">
-        <v>146.55</v>
+        <v>450</v>
       </c>
     </row>
     <row r="40" ht="23" customHeight="1">
@@ -2708,19 +2768,19 @@
         <v>46153</v>
       </c>
       <c r="C40" s="7">
-        <v>46139</v>
+        <v>46153</v>
       </c>
       <c r="D40" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>23</v>
+        <v>46153</v>
+      </c>
+      <c r="E40" s="7">
+        <v>46119</v>
       </c>
       <c r="F40" s="8">
-        <v>-23</v>
+        <v>-3</v>
       </c>
       <c r="G40" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>25</v>
@@ -2729,16 +2789,16 @@
         <v>25</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="N40" s="6" t="s">
         <v>28</v>
@@ -2750,13 +2810,13 @@
         <v>23</v>
       </c>
       <c r="Q40" s="6" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="R40" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S40" s="9">
-        <v>450</v>
+        <v>600</v>
       </c>
     </row>
     <row r="41" ht="23" customHeight="1">
@@ -2773,13 +2833,13 @@
         <v>46153</v>
       </c>
       <c r="E41" s="7">
-        <v>46119</v>
+        <v>46127</v>
       </c>
       <c r="F41" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G41" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>25</v>
@@ -2788,16 +2848,16 @@
         <v>25</v>
       </c>
       <c r="J41" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L41" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="K41" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L41" s="6" t="s">
-        <v>48</v>
-      </c>
       <c r="M41" s="6" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="N41" s="6" t="s">
         <v>28</v>
@@ -2832,13 +2892,13 @@
         <v>46153</v>
       </c>
       <c r="E42" s="7">
-        <v>46127</v>
+        <v>46141</v>
       </c>
       <c r="F42" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G42" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>25</v>
@@ -2853,10 +2913,10 @@
         <v>23</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="N42" s="6" t="s">
         <v>28</v>
@@ -2874,7 +2934,7 @@
         <v>30</v>
       </c>
       <c r="S42" s="9">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="43" ht="23" customHeight="1">
@@ -2891,13 +2951,13 @@
         <v>46153</v>
       </c>
       <c r="E43" s="7">
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="F43" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G43" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H43" s="6" t="s">
         <v>25</v>
@@ -2906,16 +2966,16 @@
         <v>25</v>
       </c>
       <c r="J43" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L43" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="K43" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L43" s="6" t="s">
-        <v>89</v>
-      </c>
       <c r="M43" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N43" s="6" t="s">
         <v>28</v>
@@ -2930,7 +2990,7 @@
         <v>39</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S43" s="9">
         <v>620</v>
@@ -2950,13 +3010,13 @@
         <v>46153</v>
       </c>
       <c r="E44" s="7">
-        <v>46141</v>
+        <v>46119</v>
       </c>
       <c r="F44" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G44" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>25</v>
@@ -2965,16 +3025,16 @@
         <v>25</v>
       </c>
       <c r="J44" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L44" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="K44" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L44" s="6" t="s">
-        <v>61</v>
-      </c>
       <c r="M44" s="6" t="s">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="N44" s="6" t="s">
         <v>28</v>
@@ -2989,7 +3049,7 @@
         <v>39</v>
       </c>
       <c r="R44" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S44" s="9">
         <v>620</v>
@@ -3009,13 +3069,13 @@
         <v>46153</v>
       </c>
       <c r="E45" s="7">
-        <v>46141</v>
+        <v>46127</v>
       </c>
       <c r="F45" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G45" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H45" s="6" t="s">
         <v>25</v>
@@ -3033,7 +3093,7 @@
         <v>92</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="N45" s="6" t="s">
         <v>28</v>
@@ -3051,7 +3111,7 @@
         <v>30</v>
       </c>
       <c r="S45" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="46" ht="23" customHeight="1">
@@ -3068,13 +3128,13 @@
         <v>46153</v>
       </c>
       <c r="E46" s="7">
-        <v>46150</v>
+        <v>46112</v>
       </c>
       <c r="F46" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G46" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>25</v>
@@ -3089,7 +3149,7 @@
         <v>23</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="M46" s="6" t="s">
         <v>23</v>
@@ -3127,13 +3187,13 @@
         <v>46153</v>
       </c>
       <c r="E47" s="7">
-        <v>46127</v>
+        <v>46150</v>
       </c>
       <c r="F47" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G47" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H47" s="6" t="s">
         <v>25</v>
@@ -3186,13 +3246,13 @@
         <v>46153</v>
       </c>
       <c r="E48" s="7">
-        <v>46112</v>
+        <v>46092</v>
       </c>
       <c r="F48" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G48" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>25</v>
@@ -3228,7 +3288,7 @@
         <v>30</v>
       </c>
       <c r="S48" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="49" ht="23" customHeight="1">
@@ -3245,13 +3305,13 @@
         <v>46153</v>
       </c>
       <c r="E49" s="7">
-        <v>46112</v>
+        <v>46119</v>
       </c>
       <c r="F49" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G49" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H49" s="6" t="s">
         <v>25</v>
@@ -3266,10 +3326,10 @@
         <v>23</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="N49" s="6" t="s">
         <v>28</v>
@@ -3287,7 +3347,7 @@
         <v>30</v>
       </c>
       <c r="S49" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="50" ht="23" customHeight="1">
@@ -3304,13 +3364,13 @@
         <v>46153</v>
       </c>
       <c r="E50" s="7">
-        <v>46092</v>
+        <v>46119</v>
       </c>
       <c r="F50" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G50" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H50" s="6" t="s">
         <v>25</v>
@@ -3346,7 +3406,7 @@
         <v>30</v>
       </c>
       <c r="S50" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="51" ht="23" customHeight="1">
@@ -3366,10 +3426,10 @@
         <v>46119</v>
       </c>
       <c r="F51" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G51" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H51" s="6" t="s">
         <v>25</v>
@@ -3384,10 +3444,10 @@
         <v>23</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="M51" s="6" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="N51" s="6" t="s">
         <v>28</v>
@@ -3402,10 +3462,10 @@
         <v>39</v>
       </c>
       <c r="R51" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S51" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="52" ht="23" customHeight="1">
@@ -3422,13 +3482,13 @@
         <v>46153</v>
       </c>
       <c r="E52" s="7">
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="F52" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G52" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>25</v>
@@ -3461,7 +3521,7 @@
         <v>39</v>
       </c>
       <c r="R52" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S52" s="9">
         <v>680</v>
@@ -3481,13 +3541,13 @@
         <v>46153</v>
       </c>
       <c r="E53" s="7">
-        <v>46119</v>
+        <v>46092</v>
       </c>
       <c r="F53" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G53" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H53" s="6" t="s">
         <v>25</v>
@@ -3502,7 +3562,7 @@
         <v>23</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>32</v>
+        <v>105</v>
       </c>
       <c r="M53" s="6" t="s">
         <v>23</v>
@@ -3520,10 +3580,10 @@
         <v>39</v>
       </c>
       <c r="R53" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S53" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="54" ht="23" customHeight="1">
@@ -3540,13 +3600,13 @@
         <v>46153</v>
       </c>
       <c r="E54" s="7">
-        <v>46141</v>
+        <v>46119</v>
       </c>
       <c r="F54" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G54" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H54" s="6" t="s">
         <v>25</v>
@@ -3555,13 +3615,13 @@
         <v>25</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="M54" s="6" t="s">
         <v>23</v>
@@ -3573,16 +3633,16 @@
         <v>28</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q54" s="6" t="s">
         <v>39</v>
       </c>
       <c r="R54" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S54" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="55" ht="23" customHeight="1">
@@ -3590,19 +3650,19 @@
         <v>22</v>
       </c>
       <c r="B55" s="7">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C55" s="7">
-        <v>46153</v>
+        <v>46146</v>
       </c>
       <c r="D55" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E55" s="7">
-        <v>46092</v>
+        <v>46146</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F55" s="8">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="G55" s="8">
         <v>-2</v>
@@ -3620,7 +3680,7 @@
         <v>23</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="M55" s="6" t="s">
         <v>23</v>
@@ -3635,13 +3695,13 @@
         <v>23</v>
       </c>
       <c r="Q55" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R55" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S55" s="9">
-        <v>700</v>
+        <v>280</v>
       </c>
     </row>
     <row r="56" ht="23" customHeight="1">
@@ -3649,19 +3709,19 @@
         <v>22</v>
       </c>
       <c r="B56" s="7">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C56" s="7">
-        <v>46153</v>
+        <v>46132</v>
       </c>
       <c r="D56" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E56" s="7">
-        <v>46119</v>
+        <v>46132</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F56" s="8">
-        <v>-2</v>
+        <v>-24</v>
       </c>
       <c r="G56" s="8">
         <v>-2</v>
@@ -3673,16 +3733,16 @@
         <v>25</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K56" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="N56" s="6" t="s">
         <v>28</v>
@@ -3691,16 +3751,16 @@
         <v>28</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q56" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R56" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S56" s="9">
-        <v>700</v>
+        <v>317.54</v>
       </c>
     </row>
     <row r="57" ht="23" customHeight="1">
@@ -3708,58 +3768,58 @@
         <v>22</v>
       </c>
       <c r="B57" s="7">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="C57" s="7">
-        <v>46132</v>
+        <v>46082</v>
       </c>
       <c r="D57" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>23</v>
+        <v>46160</v>
+      </c>
+      <c r="E57" s="7">
+        <v>46097</v>
       </c>
       <c r="F57" s="8">
-        <v>-23</v>
+        <v>4</v>
       </c>
       <c r="G57" s="8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="K57" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="M57" s="6" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="N57" s="6" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="O57" s="6" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="P57" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q57" s="6" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="R57" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S57" s="9">
-        <v>317.54</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="58" ht="23" customHeight="1">
@@ -3770,19 +3830,19 @@
         <v>46160</v>
       </c>
       <c r="C58" s="7">
-        <v>46082</v>
+        <v>46160</v>
       </c>
       <c r="D58" s="7">
         <v>46160</v>
       </c>
       <c r="E58" s="7">
-        <v>46097</v>
+        <v>46112</v>
       </c>
       <c r="F58" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G58" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H58" s="6" t="s">
         <v>23</v>
@@ -3791,34 +3851,34 @@
         <v>23</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="K58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>32</v>
+        <v>111</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>23</v>
+        <v>111</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q58" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R58" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S58" s="9">
-        <v>146.55</v>
+        <v>600</v>
       </c>
     </row>
     <row r="59" ht="23" customHeight="1">
@@ -3838,10 +3898,10 @@
         <v>46119</v>
       </c>
       <c r="F59" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G59" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H59" s="6" t="s">
         <v>23</v>
@@ -3862,10 +3922,10 @@
         <v>48</v>
       </c>
       <c r="N59" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O59" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P59" s="6" t="s">
         <v>23</v>
@@ -3894,13 +3954,13 @@
         <v>46160</v>
       </c>
       <c r="E60" s="7">
-        <v>46112</v>
+        <v>46127</v>
       </c>
       <c r="F60" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G60" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H60" s="6" t="s">
         <v>23</v>
@@ -3915,16 +3975,16 @@
         <v>23</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>23</v>
@@ -3953,13 +4013,13 @@
         <v>46160</v>
       </c>
       <c r="E61" s="7">
-        <v>46127</v>
+        <v>46141</v>
       </c>
       <c r="F61" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G61" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H61" s="6" t="s">
         <v>23</v>
@@ -3968,22 +4028,22 @@
         <v>23</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="M61" s="6" t="s">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="N61" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P61" s="6" t="s">
         <v>23</v>
@@ -3995,7 +4055,7 @@
         <v>30</v>
       </c>
       <c r="S61" s="9">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="62" ht="23" customHeight="1">
@@ -4012,13 +4072,13 @@
         <v>46160</v>
       </c>
       <c r="E62" s="7">
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="F62" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G62" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H62" s="6" t="s">
         <v>23</v>
@@ -4027,22 +4087,22 @@
         <v>23</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>23</v>
@@ -4051,7 +4111,7 @@
         <v>39</v>
       </c>
       <c r="R62" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S62" s="9">
         <v>620</v>
@@ -4071,13 +4131,13 @@
         <v>46160</v>
       </c>
       <c r="E63" s="7">
-        <v>46141</v>
+        <v>46119</v>
       </c>
       <c r="F63" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G63" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H63" s="6" t="s">
         <v>23</v>
@@ -4086,22 +4146,22 @@
         <v>23</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K63" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="M63" s="6" t="s">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="N63" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P63" s="6" t="s">
         <v>23</v>
@@ -4110,7 +4170,7 @@
         <v>39</v>
       </c>
       <c r="R63" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S63" s="9">
         <v>620</v>
@@ -4130,13 +4190,13 @@
         <v>46160</v>
       </c>
       <c r="E64" s="7">
-        <v>46141</v>
+        <v>46112</v>
       </c>
       <c r="F64" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G64" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H64" s="6" t="s">
         <v>23</v>
@@ -4145,22 +4205,22 @@
         <v>23</v>
       </c>
       <c r="J64" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="K64" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L64" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="K64" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L64" s="6" t="s">
-        <v>92</v>
-      </c>
       <c r="M64" s="6" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>23</v>
@@ -4172,7 +4232,7 @@
         <v>30</v>
       </c>
       <c r="S64" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="65" ht="23" customHeight="1">
@@ -4189,13 +4249,13 @@
         <v>46160</v>
       </c>
       <c r="E65" s="7">
-        <v>46150</v>
+        <v>46112</v>
       </c>
       <c r="F65" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G65" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H65" s="6" t="s">
         <v>23</v>
@@ -4210,16 +4270,16 @@
         <v>23</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="M65" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N65" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O65" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P65" s="6" t="s">
         <v>23</v>
@@ -4248,13 +4308,13 @@
         <v>46160</v>
       </c>
       <c r="E66" s="7">
-        <v>46127</v>
+        <v>46119</v>
       </c>
       <c r="F66" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G66" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H66" s="6" t="s">
         <v>23</v>
@@ -4269,19 +4329,19 @@
         <v>23</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="M66" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q66" s="6" t="s">
         <v>39</v>
@@ -4307,13 +4367,13 @@
         <v>46160</v>
       </c>
       <c r="E67" s="7">
-        <v>46119</v>
+        <v>46127</v>
       </c>
       <c r="F67" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G67" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H67" s="6" t="s">
         <v>23</v>
@@ -4322,25 +4382,25 @@
         <v>23</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K67" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="M67" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N67" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O67" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P67" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q67" s="6" t="s">
         <v>39</v>
@@ -4366,13 +4426,13 @@
         <v>46160</v>
       </c>
       <c r="E68" s="7">
-        <v>46112</v>
+        <v>46150</v>
       </c>
       <c r="F68" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G68" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H68" s="6" t="s">
         <v>23</v>
@@ -4387,16 +4447,16 @@
         <v>23</v>
       </c>
       <c r="L68" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M68" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>23</v>
@@ -4425,13 +4485,13 @@
         <v>46160</v>
       </c>
       <c r="E69" s="7">
-        <v>46112</v>
+        <v>46153</v>
       </c>
       <c r="F69" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G69" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H69" s="6" t="s">
         <v>23</v>
@@ -4446,16 +4506,16 @@
         <v>23</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="M69" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N69" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O69" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P69" s="6" t="s">
         <v>23</v>
@@ -4467,7 +4527,7 @@
         <v>30</v>
       </c>
       <c r="S69" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="70" ht="23" customHeight="1">
@@ -4484,13 +4544,13 @@
         <v>46160</v>
       </c>
       <c r="E70" s="7">
-        <v>46092</v>
+        <v>46127</v>
       </c>
       <c r="F70" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G70" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H70" s="6" t="s">
         <v>23</v>
@@ -4505,16 +4565,16 @@
         <v>23</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="M70" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>23</v>
@@ -4543,13 +4603,13 @@
         <v>46160</v>
       </c>
       <c r="E71" s="7">
-        <v>46127</v>
+        <v>46092</v>
       </c>
       <c r="F71" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G71" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H71" s="6" t="s">
         <v>23</v>
@@ -4558,22 +4618,22 @@
         <v>23</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="M71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N71" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O71" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P71" s="6" t="s">
         <v>23</v>
@@ -4605,10 +4665,10 @@
         <v>46119</v>
       </c>
       <c r="F72" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G72" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H72" s="6" t="s">
         <v>23</v>
@@ -4629,10 +4689,10 @@
         <v>55</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>23</v>
@@ -4661,13 +4721,13 @@
         <v>46160</v>
       </c>
       <c r="E73" s="7">
-        <v>46153</v>
+        <v>46119</v>
       </c>
       <c r="F73" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G73" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H73" s="6" t="s">
         <v>23</v>
@@ -4682,16 +4742,16 @@
         <v>23</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>81</v>
+        <v>130</v>
       </c>
       <c r="M73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N73" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O73" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P73" s="6" t="s">
         <v>23</v>
@@ -4703,7 +4763,7 @@
         <v>30</v>
       </c>
       <c r="S73" s="9">
-        <v>650</v>
+        <v>670</v>
       </c>
     </row>
     <row r="74" ht="23" customHeight="1">
@@ -4723,10 +4783,10 @@
         <v>46119</v>
       </c>
       <c r="F74" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G74" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H74" s="6" t="s">
         <v>23</v>
@@ -4735,22 +4795,22 @@
         <v>23</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="M74" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>23</v>
@@ -4762,7 +4822,7 @@
         <v>30</v>
       </c>
       <c r="S74" s="9">
-        <v>670</v>
+        <v>680</v>
       </c>
     </row>
     <row r="75" ht="23" customHeight="1">
@@ -4779,13 +4839,13 @@
         <v>46160</v>
       </c>
       <c r="E75" s="7">
-        <v>46141</v>
+        <v>46119</v>
       </c>
       <c r="F75" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G75" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H75" s="6" t="s">
         <v>23</v>
@@ -4800,16 +4860,16 @@
         <v>23</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>106</v>
+        <v>32</v>
       </c>
       <c r="M75" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N75" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O75" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P75" s="6" t="s">
         <v>23</v>
@@ -4838,13 +4898,13 @@
         <v>46160</v>
       </c>
       <c r="E76" s="7">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="F76" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G76" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H76" s="6" t="s">
         <v>23</v>
@@ -4859,16 +4919,16 @@
         <v>23</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>23</v>
@@ -4897,13 +4957,13 @@
         <v>46160</v>
       </c>
       <c r="E77" s="7">
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="F77" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G77" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>23</v>
@@ -4918,16 +4978,16 @@
         <v>23</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>32</v>
+        <v>103</v>
       </c>
       <c r="M77" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N77" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O77" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P77" s="6" t="s">
         <v>23</v>
@@ -4956,13 +5016,13 @@
         <v>46160</v>
       </c>
       <c r="E78" s="7">
-        <v>46113</v>
+        <v>46119</v>
       </c>
       <c r="F78" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G78" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H78" s="6" t="s">
         <v>23</v>
@@ -4977,19 +5037,19 @@
         <v>23</v>
       </c>
       <c r="L78" s="6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M78" s="6" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q78" s="6" t="s">
         <v>39</v>
@@ -4998,7 +5058,7 @@
         <v>30</v>
       </c>
       <c r="S78" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="79" ht="23" customHeight="1">
@@ -5015,13 +5075,13 @@
         <v>46160</v>
       </c>
       <c r="E79" s="7">
-        <v>46092</v>
+        <v>46099</v>
       </c>
       <c r="F79" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G79" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H79" s="6" t="s">
         <v>23</v>
@@ -5036,16 +5096,16 @@
         <v>23</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="M79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N79" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O79" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P79" s="6" t="s">
         <v>23</v>
@@ -5054,7 +5114,7 @@
         <v>39</v>
       </c>
       <c r="R79" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S79" s="9">
         <v>700</v>
@@ -5074,13 +5134,13 @@
         <v>46160</v>
       </c>
       <c r="E80" s="7">
-        <v>46099</v>
+        <v>46092</v>
       </c>
       <c r="F80" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G80" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H80" s="6" t="s">
         <v>23</v>
@@ -5089,22 +5149,22 @@
         <v>23</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L80" s="6" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="M80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>23</v>
@@ -5113,7 +5173,7 @@
         <v>39</v>
       </c>
       <c r="R80" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S80" s="9">
         <v>700</v>
@@ -5124,25 +5184,25 @@
         <v>22</v>
       </c>
       <c r="B81" s="7">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="C81" s="7">
-        <v>46160</v>
+        <v>46113</v>
       </c>
       <c r="D81" s="7">
-        <v>46160</v>
+        <v>46150</v>
       </c>
       <c r="E81" s="7">
-        <v>46119</v>
+        <v>46149</v>
       </c>
       <c r="F81" s="8">
-        <v>5</v>
+        <v>-6</v>
       </c>
       <c r="G81" s="8">
         <v>5</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I81" s="6" t="s">
         <v>23</v>
@@ -5154,19 +5214,19 @@
         <v>23</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="M81" s="6" t="s">
-        <v>23</v>
+        <v>140</v>
       </c>
       <c r="N81" s="6" t="s">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="O81" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P81" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q81" s="6" t="s">
         <v>39</v>
@@ -5175,66 +5235,1187 @@
         <v>30</v>
       </c>
       <c r="S81" s="9">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="82" ht="23" customHeight="1">
+      <c r="A82" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B82" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C82" s="7">
+        <v>46082</v>
+      </c>
+      <c r="D82" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E82" s="7">
+        <v>46097</v>
+      </c>
+      <c r="F82" s="8">
+        <v>11</v>
+      </c>
+      <c r="G82" s="8">
+        <v>11</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I82" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J82" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K82" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L82" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M82" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N82" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="O82" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="P82" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q82" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="R82" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="S82" s="9">
+        <v>146.55</v>
+      </c>
+    </row>
+    <row r="83" ht="23" customHeight="1">
+      <c r="A83" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B83" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C83" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D83" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E83" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F83" s="8">
+        <v>11</v>
+      </c>
+      <c r="G83" s="8">
+        <v>11</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I83" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J83" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="K83" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L83" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M83" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N83" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="O83" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="P83" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q83" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R83" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S83" s="9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="84" ht="23" customHeight="1">
+      <c r="A84" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B84" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C84" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D84" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E84" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F84" s="8">
+        <v>11</v>
+      </c>
+      <c r="G84" s="8">
+        <v>11</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I84" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J84" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="K84" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L84" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="M84" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N84" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="O84" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="P84" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q84" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R84" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S84" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="85" ht="23" customHeight="1">
+      <c r="A85" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B85" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C85" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D85" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E85" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F85" s="8">
+        <v>11</v>
+      </c>
+      <c r="G85" s="8">
+        <v>11</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I85" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J85" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="K85" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L85" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="M85" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="N85" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="O85" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="P85" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q85" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R85" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S85" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="86" ht="23" customHeight="1">
+      <c r="A86" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B86" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C86" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D86" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E86" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F86" s="8">
+        <v>11</v>
+      </c>
+      <c r="G86" s="8">
+        <v>11</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I86" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J86" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="K86" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L86" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="M86" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="N86" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="O86" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="P86" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q86" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R86" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="S86" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="87" ht="23" customHeight="1">
+      <c r="A87" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B87" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C87" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D87" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E87" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F87" s="8">
+        <v>11</v>
+      </c>
+      <c r="G87" s="8">
+        <v>11</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I87" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J87" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="K87" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L87" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="M87" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N87" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="O87" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="P87" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q87" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R87" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S87" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="88" ht="23" customHeight="1">
+      <c r="A88" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B88" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C88" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D88" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E88" s="7">
+        <v>46150</v>
+      </c>
+      <c r="F88" s="8">
+        <v>11</v>
+      </c>
+      <c r="G88" s="8">
+        <v>11</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I88" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J88" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K88" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L88" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="M88" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N88" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="O88" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="P88" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q88" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R88" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S88" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="89" ht="23" customHeight="1">
+      <c r="A89" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B89" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C89" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D89" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E89" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F89" s="8">
+        <v>11</v>
+      </c>
+      <c r="G89" s="8">
+        <v>11</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I89" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J89" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="K89" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L89" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="M89" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N89" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="O89" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="P89" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q89" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R89" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S89" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="90" ht="23" customHeight="1">
+      <c r="A90" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B90" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C90" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D90" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E90" s="7">
+        <v>46127</v>
+      </c>
+      <c r="F90" s="8">
+        <v>11</v>
+      </c>
+      <c r="G90" s="8">
+        <v>11</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I90" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J90" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="K90" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L90" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="M90" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N90" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="O90" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="P90" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q90" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R90" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S90" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="91" ht="23" customHeight="1">
+      <c r="A91" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B91" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C91" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D91" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E91" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F91" s="8">
+        <v>11</v>
+      </c>
+      <c r="G91" s="8">
+        <v>11</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I91" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J91" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="K91" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L91" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="M91" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="N91" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="O91" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="P91" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q91" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R91" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S91" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="92" ht="23" customHeight="1">
+      <c r="A92" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B92" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C92" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D92" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E92" s="7">
+        <v>46092</v>
+      </c>
+      <c r="F92" s="8">
+        <v>11</v>
+      </c>
+      <c r="G92" s="8">
+        <v>11</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I92" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J92" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="K92" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L92" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="M92" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N92" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="O92" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="P92" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q92" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R92" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S92" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="93" ht="23" customHeight="1">
+      <c r="A93" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B93" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C93" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D93" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E93" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F93" s="8">
+        <v>11</v>
+      </c>
+      <c r="G93" s="8">
+        <v>11</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I93" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J93" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="K93" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L93" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="M93" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N93" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="O93" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="P93" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q93" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R93" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S93" s="9">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="94" ht="23" customHeight="1">
+      <c r="A94" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B94" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C94" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D94" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E94" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F94" s="8">
+        <v>11</v>
+      </c>
+      <c r="G94" s="8">
+        <v>11</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I94" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J94" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="K94" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L94" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="M94" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N94" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="O94" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="P94" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q94" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R94" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S94" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="95" ht="23" customHeight="1">
+      <c r="A95" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B95" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C95" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D95" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E95" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F95" s="8">
+        <v>11</v>
+      </c>
+      <c r="G95" s="8">
+        <v>11</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I95" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J95" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="K95" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L95" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M95" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N95" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="O95" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="P95" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q95" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R95" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="S95" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="96" ht="23" customHeight="1">
+      <c r="A96" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B96" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C96" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D96" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E96" s="7">
+        <v>46113</v>
+      </c>
+      <c r="F96" s="8">
+        <v>11</v>
+      </c>
+      <c r="G96" s="8">
+        <v>11</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I96" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J96" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="K96" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L96" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M96" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="N96" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="O96" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="P96" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q96" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R96" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S96" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="97" ht="23" customHeight="1">
+      <c r="A97" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B97" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C97" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D97" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E97" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F97" s="8">
+        <v>11</v>
+      </c>
+      <c r="G97" s="8">
+        <v>11</v>
+      </c>
+      <c r="H97" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I97" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J97" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="K97" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L97" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="M97" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N97" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="O97" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="P97" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q97" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R97" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="S97" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="98" ht="23" customHeight="1">
+      <c r="A98" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B98" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C98" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D98" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E98" s="7">
+        <v>46099</v>
+      </c>
+      <c r="F98" s="8">
+        <v>11</v>
+      </c>
+      <c r="G98" s="8">
+        <v>11</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I98" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J98" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="K98" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L98" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="M98" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N98" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="O98" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="P98" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q98" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R98" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="S98" s="9">
         <v>700</v>
       </c>
     </row>
-    <row r="82" ht="23" customHeight="1">
-      <c r="A82" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B82" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C82" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D82" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E82" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F82" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G82" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H82" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I82" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J82" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="K82" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="L82" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M82" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="N82" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="O82" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="P82" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q82" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="R82" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="S82" s="13">
-        <f>SUM(S6:S81)</f>
+    <row r="99" ht="23" customHeight="1">
+      <c r="A99" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B99" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C99" s="7">
+        <v>46113</v>
+      </c>
+      <c r="D99" s="7">
+        <v>46150</v>
+      </c>
+      <c r="E99" s="7">
+        <v>46149</v>
+      </c>
+      <c r="F99" s="8">
+        <v>-6</v>
+      </c>
+      <c r="G99" s="8">
+        <v>11</v>
+      </c>
+      <c r="H99" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I99" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J99" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="K99" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L99" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="M99" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="N99" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="O99" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="P99" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q99" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R99" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S99" s="9">
+        <v>4400</v>
+      </c>
+    </row>
+    <row r="100" ht="23" customHeight="1">
+      <c r="A100" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B100" s="7">
+        <v>46172</v>
+      </c>
+      <c r="C100" s="7">
+        <v>45930</v>
+      </c>
+      <c r="D100" s="7">
+        <v>46172</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F100" s="8">
+        <v>16</v>
+      </c>
+      <c r="G100" s="8">
+        <v>16</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I100" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J100" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K100" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L100" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M100" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N100" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="O100" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="P100" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q100" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R100" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="S100" s="9">
+        <v>185.5</v>
+      </c>
+    </row>
+    <row r="101" ht="23" customHeight="1">
+      <c r="A101" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B101" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C101" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D101" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E101" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F101" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G101" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H101" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I101" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J101" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K101" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L101" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M101" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="N101" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="O101" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="P101" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q101" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="R101" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S101" s="13">
+        <f>SUM(S6:S100)</f>
       </c>
     </row>
   </sheetData>
